--- a/data/supply_teachers/rm6376/Supplier details.xlsx
+++ b/data/supply_teachers/rm6376/Supplier details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timothy.south/Code/crown-marketplace-runner/code/testing/crown-marketplace-feature-tests/data/supply_teachers/rm6376/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DAE11A-7CCB-A949-BE76-F518940A657B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E001FD-53A5-B941-949F-4D976493C57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
   <si>
     <t>Supplier Name</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>Managed service provider contact telephone</t>
+  </si>
+  <si>
+    <t>Accredited supplier</t>
   </si>
 </sst>
 </file>
@@ -592,7 +595,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:V999"/>
+  <dimension ref="A1:W999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.1640625" customWidth="1"/>
@@ -600,12 +603,12 @@
     <col min="3" max="3" width="19.6640625" style="13" customWidth="1"/>
     <col min="4" max="4" width="24" style="13" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" style="13" customWidth="1"/>
-    <col min="6" max="6" width="25.1640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" style="10" customWidth="1"/>
+    <col min="6" max="7" width="25.1640625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,13 +627,15 @@
       <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -642,10 +647,11 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
-      <c r="U1" s="3"/>
+      <c r="U1" s="2"/>
       <c r="V1" s="3"/>
-    </row>
-    <row r="2" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W1" s="3"/>
+    </row>
+    <row r="2" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -661,8 +667,10 @@
       <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="7"/>
+      <c r="H2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="15"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
@@ -676,8 +684,9 @@
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
-    </row>
-    <row r="3" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W2" s="7"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -690,11 +699,13 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="8"/>
+      <c r="H3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="16"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
@@ -708,8 +719,9 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8"/>
-    </row>
-    <row r="4" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W3" s="8"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -731,10 +743,12 @@
       <c r="G4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="7"/>
+      <c r="I4" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -748,8 +762,9 @@
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
-    </row>
-    <row r="5" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W4" s="7"/>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -765,8 +780,10 @@
       <c r="G5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="7"/>
+      <c r="H5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="15"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
@@ -780,8 +797,9 @@
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
-    </row>
-    <row r="6" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W5" s="7"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -797,8 +815,10 @@
       <c r="G6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="7"/>
+      <c r="H6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="15"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
@@ -812,8 +832,9 @@
       <c r="T6" s="7"/>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
-    </row>
-    <row r="7" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W6" s="7"/>
+    </row>
+    <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
@@ -829,8 +850,10 @@
       <c r="G7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="7"/>
+      <c r="H7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="15"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
@@ -844,8 +867,9 @@
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
-    </row>
-    <row r="8" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W7" s="7"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -867,10 +891,12 @@
       <c r="G8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="7"/>
+      <c r="I8" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -884,8 +910,9 @@
       <c r="T8" s="7"/>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
-    </row>
-    <row r="9" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W8" s="7"/>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>27</v>
       </c>
@@ -904,11 +931,13 @@
       <c r="F9" s="11">
         <v>50960663100</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="15" t="s">
+      <c r="G9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="7"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -922,8 +951,9 @@
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
-    </row>
-    <row r="10" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W9" s="7"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
@@ -942,11 +972,13 @@
       <c r="F10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="15" t="s">
+      <c r="G10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="7"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -960,8 +992,9 @@
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
-    </row>
-    <row r="11" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W10" s="7"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>36</v>
       </c>
@@ -977,8 +1010,10 @@
       <c r="G11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="7"/>
+      <c r="H11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="15"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
@@ -992,8 +1027,9 @@
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
-    </row>
-    <row r="12" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W11" s="7"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
@@ -1009,8 +1045,10 @@
       <c r="G12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="7"/>
+      <c r="H12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="15"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -1024,8 +1062,9 @@
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
-    </row>
-    <row r="13" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W12" s="7"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>40</v>
       </c>
@@ -1044,11 +1083,13 @@
       <c r="F13" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="15" t="s">
+      <c r="G13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="7"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -1062,8 +1103,9 @@
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
-    </row>
-    <row r="14" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W13" s="7"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>46</v>
       </c>
@@ -1079,8 +1121,10 @@
       <c r="G14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="7"/>
+      <c r="H14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="15"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -1094,8 +1138,9 @@
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
-    </row>
-    <row r="15" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W14" s="7"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>49</v>
       </c>
@@ -1111,8 +1156,10 @@
       <c r="G15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="7"/>
+      <c r="H15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="15"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -1126,8 +1173,9 @@
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
-    </row>
-    <row r="16" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W15" s="7"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
@@ -1143,8 +1191,10 @@
       <c r="G16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="7"/>
+      <c r="H16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="15"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -1158,8 +1208,9 @@
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
-    </row>
-    <row r="17" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W16" s="7"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>54</v>
       </c>
@@ -1175,8 +1226,10 @@
       <c r="G17" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="7"/>
+      <c r="H17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="15"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -1190,8 +1243,9 @@
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
-    </row>
-    <row r="18" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W17" s="7"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>56</v>
       </c>
@@ -1207,8 +1261,10 @@
       <c r="G18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="7"/>
+      <c r="H18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="15"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -1222,8 +1278,9 @@
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
-    </row>
-    <row r="19" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W18" s="7"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>59</v>
       </c>
@@ -1239,8 +1296,10 @@
       <c r="G19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="7"/>
+      <c r="H19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="15"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -1254,17 +1313,18 @@
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
-    </row>
-    <row r="20" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W19" s="7"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="7"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="15"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -1278,17 +1338,18 @@
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
-    </row>
-    <row r="21" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W20" s="7"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="7"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="15"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -1302,17 +1363,18 @@
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
-    </row>
-    <row r="22" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W21" s="7"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="7"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="15"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -1326,17 +1388,18 @@
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
-    </row>
-    <row r="23" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W22" s="7"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="7"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="15"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -1350,17 +1413,18 @@
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
-    </row>
-    <row r="24" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W23" s="7"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="7"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="15"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -1374,17 +1438,18 @@
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
-    </row>
-    <row r="25" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W24" s="7"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="7"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="15"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -1398,17 +1463,18 @@
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
-    </row>
-    <row r="26" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W25" s="7"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="7"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="15"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -1422,17 +1488,18 @@
       <c r="T26" s="7"/>
       <c r="U26" s="7"/>
       <c r="V26" s="7"/>
-    </row>
-    <row r="27" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W26" s="7"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="7"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="15"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -1446,17 +1513,18 @@
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
-    </row>
-    <row r="28" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W27" s="7"/>
+    </row>
+    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="7"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="15"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -1470,17 +1538,18 @@
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
-    </row>
-    <row r="29" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W28" s="7"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="7"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="15"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -1494,17 +1563,18 @@
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
-    </row>
-    <row r="30" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W29" s="7"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="7"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="15"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -1518,17 +1588,18 @@
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
       <c r="V30" s="7"/>
-    </row>
-    <row r="31" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W30" s="7"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="7"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="15"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -1542,17 +1613,18 @@
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
-    </row>
-    <row r="32" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W31" s="7"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="7"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="15"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -1566,17 +1638,18 @@
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
-    </row>
-    <row r="33" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W32" s="7"/>
+    </row>
+    <row r="33" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="7"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="15"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -1590,17 +1663,18 @@
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
-    </row>
-    <row r="34" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W33" s="7"/>
+    </row>
+    <row r="34" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="7"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="15"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -1614,17 +1688,18 @@
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
-    </row>
-    <row r="35" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W34" s="7"/>
+    </row>
+    <row r="35" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="7"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="15"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -1638,17 +1713,18 @@
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
-    </row>
-    <row r="36" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W35" s="7"/>
+    </row>
+    <row r="36" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="7"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="17"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -1662,17 +1738,18 @@
       <c r="T36" s="7"/>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>
-    </row>
-    <row r="37" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W36" s="7"/>
+    </row>
+    <row r="37" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="7"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="17"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -1686,17 +1763,18 @@
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
-    </row>
-    <row r="38" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W37" s="7"/>
+    </row>
+    <row r="38" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="7"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="17"/>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -1710,17 +1788,18 @@
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7"/>
-    </row>
-    <row r="39" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W38" s="7"/>
+    </row>
+    <row r="39" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="7"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="17"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -1734,17 +1813,18 @@
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
-    </row>
-    <row r="40" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W39" s="7"/>
+    </row>
+    <row r="40" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="7"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="17"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -1758,17 +1838,18 @@
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
-    </row>
-    <row r="41" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W40" s="7"/>
+    </row>
+    <row r="41" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="7"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="17"/>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -1782,17 +1863,18 @@
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
-    </row>
-    <row r="42" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W41" s="7"/>
+    </row>
+    <row r="42" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="7"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="17"/>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -1806,17 +1888,18 @@
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
-    </row>
-    <row r="43" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W42" s="7"/>
+    </row>
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="7"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="17"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -1830,17 +1913,18 @@
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
-    </row>
-    <row r="44" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W43" s="7"/>
+    </row>
+    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="7"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="17"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -1854,17 +1938,18 @@
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
       <c r="V44" s="7"/>
-    </row>
-    <row r="45" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W44" s="7"/>
+    </row>
+    <row r="45" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="7"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="17"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -1878,17 +1963,18 @@
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
-    </row>
-    <row r="46" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W45" s="7"/>
+    </row>
+    <row r="46" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="7"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="17"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -1902,17 +1988,18 @@
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
       <c r="V46" s="7"/>
-    </row>
-    <row r="47" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W46" s="7"/>
+    </row>
+    <row r="47" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="7"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="17"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -1926,17 +2013,18 @@
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
-    </row>
-    <row r="48" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W47" s="7"/>
+    </row>
+    <row r="48" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="7"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="17"/>
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -1950,17 +2038,18 @@
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
-    </row>
-    <row r="49" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W48" s="7"/>
+    </row>
+    <row r="49" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="7"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="17"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -1974,17 +2063,18 @@
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
-    </row>
-    <row r="50" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W49" s="7"/>
+    </row>
+    <row r="50" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="7"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="17"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -1998,17 +2088,18 @@
       <c r="T50" s="7"/>
       <c r="U50" s="7"/>
       <c r="V50" s="7"/>
-    </row>
-    <row r="51" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W50" s="7"/>
+    </row>
+    <row r="51" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="7"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="17"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -2022,17 +2113,18 @@
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
-    </row>
-    <row r="52" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W51" s="7"/>
+    </row>
+    <row r="52" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="7"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="17"/>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -2046,17 +2138,18 @@
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
-    </row>
-    <row r="53" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W52" s="7"/>
+    </row>
+    <row r="53" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="7"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="17"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -2070,17 +2163,18 @@
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
       <c r="V53" s="7"/>
-    </row>
-    <row r="54" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W53" s="7"/>
+    </row>
+    <row r="54" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="7"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="17"/>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -2094,17 +2188,18 @@
       <c r="T54" s="7"/>
       <c r="U54" s="7"/>
       <c r="V54" s="7"/>
-    </row>
-    <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W54" s="7"/>
+    </row>
+    <row r="55" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="7"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="17"/>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -2118,17 +2213,18 @@
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
-    </row>
-    <row r="56" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W55" s="7"/>
+    </row>
+    <row r="56" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="7"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="17"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -2142,17 +2238,18 @@
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
       <c r="V56" s="7"/>
-    </row>
-    <row r="57" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W56" s="7"/>
+    </row>
+    <row r="57" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="4"/>
       <c r="B57" s="5"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="7"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="17"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -2166,17 +2263,18 @@
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
       <c r="V57" s="7"/>
-    </row>
-    <row r="58" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W57" s="7"/>
+    </row>
+    <row r="58" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="7"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="17"/>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -2190,17 +2288,18 @@
       <c r="T58" s="7"/>
       <c r="U58" s="7"/>
       <c r="V58" s="7"/>
-    </row>
-    <row r="59" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W58" s="7"/>
+    </row>
+    <row r="59" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="7"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="17"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -2214,17 +2313,18 @@
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
-    </row>
-    <row r="60" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W59" s="7"/>
+    </row>
+    <row r="60" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="7"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="17"/>
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -2238,17 +2338,18 @@
       <c r="T60" s="7"/>
       <c r="U60" s="7"/>
       <c r="V60" s="7"/>
-    </row>
-    <row r="61" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W60" s="7"/>
+    </row>
+    <row r="61" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="7"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="17"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -2262,17 +2363,18 @@
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
-    </row>
-    <row r="62" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W61" s="7"/>
+    </row>
+    <row r="62" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="7"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="17"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -2286,17 +2388,18 @@
       <c r="T62" s="7"/>
       <c r="U62" s="7"/>
       <c r="V62" s="7"/>
-    </row>
-    <row r="63" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W62" s="7"/>
+    </row>
+    <row r="63" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="7"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="17"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -2310,17 +2413,18 @@
       <c r="T63" s="7"/>
       <c r="U63" s="7"/>
       <c r="V63" s="7"/>
-    </row>
-    <row r="64" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W63" s="7"/>
+    </row>
+    <row r="64" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
       <c r="E64" s="11"/>
       <c r="F64" s="11"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="7"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="17"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -2334,17 +2438,18 @@
       <c r="T64" s="7"/>
       <c r="U64" s="7"/>
       <c r="V64" s="7"/>
-    </row>
-    <row r="65" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W64" s="7"/>
+    </row>
+    <row r="65" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
       <c r="E65" s="11"/>
       <c r="F65" s="11"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="7"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="17"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -2358,17 +2463,18 @@
       <c r="T65" s="7"/>
       <c r="U65" s="7"/>
       <c r="V65" s="7"/>
-    </row>
-    <row r="66" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W65" s="7"/>
+    </row>
+    <row r="66" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="7"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="17"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -2382,17 +2488,18 @@
       <c r="T66" s="7"/>
       <c r="U66" s="7"/>
       <c r="V66" s="7"/>
-    </row>
-    <row r="67" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W66" s="7"/>
+    </row>
+    <row r="67" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="7"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="17"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -2406,17 +2513,18 @@
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
       <c r="V67" s="7"/>
-    </row>
-    <row r="68" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W67" s="7"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="4"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
       <c r="E68" s="11"/>
       <c r="F68" s="11"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="7"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="17"/>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -2430,17 +2538,18 @@
       <c r="T68" s="7"/>
       <c r="U68" s="7"/>
       <c r="V68" s="7"/>
-    </row>
-    <row r="69" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W68" s="7"/>
+    </row>
+    <row r="69" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="11"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="7"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="17"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -2454,17 +2563,18 @@
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
-    </row>
-    <row r="70" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W69" s="7"/>
+    </row>
+    <row r="70" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
       <c r="F70" s="11"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="17"/>
-      <c r="I70" s="7"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="17"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -2478,17 +2588,18 @@
       <c r="T70" s="7"/>
       <c r="U70" s="7"/>
       <c r="V70" s="7"/>
-    </row>
-    <row r="71" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W70" s="7"/>
+    </row>
+    <row r="71" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="7"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="17"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -2502,17 +2613,18 @@
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
-    </row>
-    <row r="72" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W71" s="7"/>
+    </row>
+    <row r="72" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="9"/>
       <c r="B72" s="5"/>
       <c r="C72" s="12"/>
       <c r="D72" s="12"/>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="7"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="17"/>
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -2526,17 +2638,18 @@
       <c r="T72" s="7"/>
       <c r="U72" s="7"/>
       <c r="V72" s="7"/>
-    </row>
-    <row r="73" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W72" s="7"/>
+    </row>
+    <row r="73" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="9"/>
       <c r="B73" s="5"/>
       <c r="C73" s="12"/>
       <c r="D73" s="12"/>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="7"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="17"/>
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -2550,17 +2663,18 @@
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
-    </row>
-    <row r="74" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W73" s="7"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="9"/>
       <c r="B74" s="5"/>
       <c r="C74" s="12"/>
       <c r="D74" s="12"/>
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="7"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="17"/>
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -2574,17 +2688,18 @@
       <c r="T74" s="7"/>
       <c r="U74" s="7"/>
       <c r="V74" s="7"/>
-    </row>
-    <row r="75" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W74" s="7"/>
+    </row>
+    <row r="75" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="9"/>
       <c r="B75" s="5"/>
       <c r="C75" s="12"/>
       <c r="D75" s="12"/>
       <c r="E75" s="12"/>
       <c r="F75" s="12"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="7"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="17"/>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -2598,17 +2713,18 @@
       <c r="T75" s="7"/>
       <c r="U75" s="7"/>
       <c r="V75" s="7"/>
-    </row>
-    <row r="76" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W75" s="7"/>
+    </row>
+    <row r="76" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="9"/>
       <c r="B76" s="5"/>
       <c r="C76" s="12"/>
       <c r="D76" s="12"/>
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="17"/>
-      <c r="I76" s="7"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="17"/>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -2622,17 +2738,18 @@
       <c r="T76" s="7"/>
       <c r="U76" s="7"/>
       <c r="V76" s="7"/>
-    </row>
-    <row r="77" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W76" s="7"/>
+    </row>
+    <row r="77" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="9"/>
       <c r="B77" s="5"/>
       <c r="C77" s="12"/>
       <c r="D77" s="12"/>
       <c r="E77" s="12"/>
       <c r="F77" s="12"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="7"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="17"/>
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -2646,17 +2763,18 @@
       <c r="T77" s="7"/>
       <c r="U77" s="7"/>
       <c r="V77" s="7"/>
-    </row>
-    <row r="78" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W77" s="7"/>
+    </row>
+    <row r="78" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="9"/>
       <c r="B78" s="5"/>
       <c r="C78" s="12"/>
       <c r="D78" s="12"/>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="7"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="17"/>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -2670,17 +2788,18 @@
       <c r="T78" s="7"/>
       <c r="U78" s="7"/>
       <c r="V78" s="7"/>
-    </row>
-    <row r="79" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W78" s="7"/>
+    </row>
+    <row r="79" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="9"/>
       <c r="B79" s="5"/>
       <c r="C79" s="12"/>
       <c r="D79" s="12"/>
       <c r="E79" s="12"/>
       <c r="F79" s="12"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="7"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="17"/>
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -2694,17 +2813,18 @@
       <c r="T79" s="7"/>
       <c r="U79" s="7"/>
       <c r="V79" s="7"/>
-    </row>
-    <row r="80" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W79" s="7"/>
+    </row>
+    <row r="80" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="9"/>
       <c r="B80" s="5"/>
       <c r="C80" s="12"/>
       <c r="D80" s="12"/>
       <c r="E80" s="12"/>
       <c r="F80" s="12"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="7"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="17"/>
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -2718,17 +2838,18 @@
       <c r="T80" s="7"/>
       <c r="U80" s="7"/>
       <c r="V80" s="7"/>
-    </row>
-    <row r="81" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W80" s="7"/>
+    </row>
+    <row r="81" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="9"/>
       <c r="B81" s="5"/>
       <c r="C81" s="12"/>
       <c r="D81" s="12"/>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="7"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="17"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -2742,17 +2863,18 @@
       <c r="T81" s="7"/>
       <c r="U81" s="7"/>
       <c r="V81" s="7"/>
-    </row>
-    <row r="82" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W81" s="7"/>
+    </row>
+    <row r="82" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="9"/>
       <c r="B82" s="5"/>
       <c r="C82" s="12"/>
       <c r="D82" s="12"/>
       <c r="E82" s="12"/>
       <c r="F82" s="12"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="7"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="17"/>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -2766,17 +2888,18 @@
       <c r="T82" s="7"/>
       <c r="U82" s="7"/>
       <c r="V82" s="7"/>
-    </row>
-    <row r="83" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W82" s="7"/>
+    </row>
+    <row r="83" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="9"/>
       <c r="B83" s="5"/>
       <c r="C83" s="12"/>
       <c r="D83" s="12"/>
       <c r="E83" s="12"/>
       <c r="F83" s="12"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="7"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="17"/>
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -2790,17 +2913,18 @@
       <c r="T83" s="7"/>
       <c r="U83" s="7"/>
       <c r="V83" s="7"/>
-    </row>
-    <row r="84" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W83" s="7"/>
+    </row>
+    <row r="84" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="9"/>
       <c r="B84" s="5"/>
       <c r="C84" s="12"/>
       <c r="D84" s="12"/>
       <c r="E84" s="12"/>
       <c r="F84" s="12"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="7"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="17"/>
       <c r="J84" s="7"/>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -2814,17 +2938,18 @@
       <c r="T84" s="7"/>
       <c r="U84" s="7"/>
       <c r="V84" s="7"/>
-    </row>
-    <row r="85" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W84" s="7"/>
+    </row>
+    <row r="85" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="9"/>
       <c r="B85" s="5"/>
       <c r="C85" s="12"/>
       <c r="D85" s="12"/>
       <c r="E85" s="12"/>
       <c r="F85" s="12"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="7"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="17"/>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -2838,17 +2963,18 @@
       <c r="T85" s="7"/>
       <c r="U85" s="7"/>
       <c r="V85" s="7"/>
-    </row>
-    <row r="86" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W85" s="7"/>
+    </row>
+    <row r="86" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="9"/>
       <c r="B86" s="5"/>
       <c r="C86" s="12"/>
       <c r="D86" s="12"/>
       <c r="E86" s="12"/>
       <c r="F86" s="12"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="17"/>
-      <c r="I86" s="7"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="17"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -2862,17 +2988,18 @@
       <c r="T86" s="7"/>
       <c r="U86" s="7"/>
       <c r="V86" s="7"/>
-    </row>
-    <row r="87" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W86" s="7"/>
+    </row>
+    <row r="87" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="9"/>
       <c r="B87" s="5"/>
       <c r="C87" s="12"/>
       <c r="D87" s="12"/>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="17"/>
-      <c r="I87" s="7"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="17"/>
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -2886,17 +3013,18 @@
       <c r="T87" s="7"/>
       <c r="U87" s="7"/>
       <c r="V87" s="7"/>
-    </row>
-    <row r="88" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W87" s="7"/>
+    </row>
+    <row r="88" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="9"/>
       <c r="B88" s="5"/>
       <c r="C88" s="12"/>
       <c r="D88" s="12"/>
       <c r="E88" s="12"/>
       <c r="F88" s="12"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="17"/>
-      <c r="I88" s="7"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="17"/>
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -2910,17 +3038,18 @@
       <c r="T88" s="7"/>
       <c r="U88" s="7"/>
       <c r="V88" s="7"/>
-    </row>
-    <row r="89" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W88" s="7"/>
+    </row>
+    <row r="89" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="9"/>
       <c r="B89" s="5"/>
       <c r="C89" s="12"/>
       <c r="D89" s="12"/>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="17"/>
-      <c r="I89" s="7"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="17"/>
       <c r="J89" s="7"/>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -2934,17 +3063,18 @@
       <c r="T89" s="7"/>
       <c r="U89" s="7"/>
       <c r="V89" s="7"/>
-    </row>
-    <row r="90" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W89" s="7"/>
+    </row>
+    <row r="90" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="9"/>
       <c r="B90" s="5"/>
       <c r="C90" s="12"/>
       <c r="D90" s="12"/>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="17"/>
-      <c r="I90" s="7"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="17"/>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -2958,17 +3088,18 @@
       <c r="T90" s="7"/>
       <c r="U90" s="7"/>
       <c r="V90" s="7"/>
-    </row>
-    <row r="91" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W90" s="7"/>
+    </row>
+    <row r="91" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="9"/>
       <c r="B91" s="5"/>
       <c r="C91" s="12"/>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="7"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="17"/>
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -2982,17 +3113,18 @@
       <c r="T91" s="7"/>
       <c r="U91" s="7"/>
       <c r="V91" s="7"/>
-    </row>
-    <row r="92" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W91" s="7"/>
+    </row>
+    <row r="92" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="9"/>
       <c r="B92" s="5"/>
       <c r="C92" s="12"/>
       <c r="D92" s="12"/>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="7"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="17"/>
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -3006,17 +3138,18 @@
       <c r="T92" s="7"/>
       <c r="U92" s="7"/>
       <c r="V92" s="7"/>
-    </row>
-    <row r="93" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W92" s="7"/>
+    </row>
+    <row r="93" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="9"/>
       <c r="B93" s="5"/>
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="7"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="17"/>
       <c r="J93" s="7"/>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -3030,17 +3163,18 @@
       <c r="T93" s="7"/>
       <c r="U93" s="7"/>
       <c r="V93" s="7"/>
-    </row>
-    <row r="94" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W93" s="7"/>
+    </row>
+    <row r="94" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="9"/>
       <c r="B94" s="5"/>
       <c r="C94" s="12"/>
       <c r="D94" s="12"/>
       <c r="E94" s="12"/>
       <c r="F94" s="12"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="17"/>
-      <c r="I94" s="7"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="17"/>
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -3054,17 +3188,18 @@
       <c r="T94" s="7"/>
       <c r="U94" s="7"/>
       <c r="V94" s="7"/>
-    </row>
-    <row r="95" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W94" s="7"/>
+    </row>
+    <row r="95" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="9"/>
       <c r="B95" s="5"/>
       <c r="C95" s="12"/>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="17"/>
-      <c r="I95" s="7"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="17"/>
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -3078,17 +3213,18 @@
       <c r="T95" s="7"/>
       <c r="U95" s="7"/>
       <c r="V95" s="7"/>
-    </row>
-    <row r="96" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W95" s="7"/>
+    </row>
+    <row r="96" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="9"/>
       <c r="B96" s="5"/>
       <c r="C96" s="12"/>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="17"/>
-      <c r="I96" s="7"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="17"/>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -3102,17 +3238,18 @@
       <c r="T96" s="7"/>
       <c r="U96" s="7"/>
       <c r="V96" s="7"/>
-    </row>
-    <row r="97" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W96" s="7"/>
+    </row>
+    <row r="97" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="9"/>
       <c r="B97" s="5"/>
       <c r="C97" s="12"/>
       <c r="D97" s="12"/>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="7"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="17"/>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -3126,17 +3263,18 @@
       <c r="T97" s="7"/>
       <c r="U97" s="7"/>
       <c r="V97" s="7"/>
-    </row>
-    <row r="98" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W97" s="7"/>
+    </row>
+    <row r="98" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="9"/>
       <c r="B98" s="5"/>
       <c r="C98" s="12"/>
       <c r="D98" s="12"/>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="7"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="17"/>
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -3150,17 +3288,18 @@
       <c r="T98" s="7"/>
       <c r="U98" s="7"/>
       <c r="V98" s="7"/>
-    </row>
-    <row r="99" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W98" s="7"/>
+    </row>
+    <row r="99" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="9"/>
       <c r="B99" s="5"/>
       <c r="C99" s="12"/>
       <c r="D99" s="12"/>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="7"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="17"/>
       <c r="J99" s="7"/>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -3174,17 +3313,18 @@
       <c r="T99" s="7"/>
       <c r="U99" s="7"/>
       <c r="V99" s="7"/>
-    </row>
-    <row r="100" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W99" s="7"/>
+    </row>
+    <row r="100" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="9"/>
       <c r="B100" s="5"/>
       <c r="C100" s="12"/>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="17"/>
-      <c r="I100" s="7"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="17"/>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -3198,17 +3338,18 @@
       <c r="T100" s="7"/>
       <c r="U100" s="7"/>
       <c r="V100" s="7"/>
-    </row>
-    <row r="101" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W100" s="7"/>
+    </row>
+    <row r="101" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="9"/>
       <c r="B101" s="5"/>
       <c r="C101" s="12"/>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="17"/>
-      <c r="I101" s="7"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="17"/>
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -3222,17 +3363,18 @@
       <c r="T101" s="7"/>
       <c r="U101" s="7"/>
       <c r="V101" s="7"/>
-    </row>
-    <row r="102" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W101" s="7"/>
+    </row>
+    <row r="102" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="9"/>
       <c r="B102" s="5"/>
       <c r="C102" s="12"/>
       <c r="D102" s="12"/>
       <c r="E102" s="12"/>
       <c r="F102" s="12"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="17"/>
-      <c r="I102" s="7"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="17"/>
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -3246,17 +3388,18 @@
       <c r="T102" s="7"/>
       <c r="U102" s="7"/>
       <c r="V102" s="7"/>
-    </row>
-    <row r="103" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W102" s="7"/>
+    </row>
+    <row r="103" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="9"/>
       <c r="B103" s="5"/>
       <c r="C103" s="12"/>
       <c r="D103" s="12"/>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="17"/>
-      <c r="I103" s="7"/>
+      <c r="G103" s="12"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="17"/>
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -3270,17 +3413,18 @@
       <c r="T103" s="7"/>
       <c r="U103" s="7"/>
       <c r="V103" s="7"/>
-    </row>
-    <row r="104" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W103" s="7"/>
+    </row>
+    <row r="104" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="9"/>
       <c r="B104" s="5"/>
       <c r="C104" s="12"/>
       <c r="D104" s="12"/>
       <c r="E104" s="12"/>
       <c r="F104" s="12"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="17"/>
-      <c r="I104" s="7"/>
+      <c r="G104" s="12"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="17"/>
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -3294,17 +3438,18 @@
       <c r="T104" s="7"/>
       <c r="U104" s="7"/>
       <c r="V104" s="7"/>
-    </row>
-    <row r="105" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W104" s="7"/>
+    </row>
+    <row r="105" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="9"/>
       <c r="B105" s="5"/>
       <c r="C105" s="12"/>
       <c r="D105" s="12"/>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="17"/>
-      <c r="I105" s="7"/>
+      <c r="G105" s="12"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="17"/>
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -3318,17 +3463,18 @@
       <c r="T105" s="7"/>
       <c r="U105" s="7"/>
       <c r="V105" s="7"/>
-    </row>
-    <row r="106" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W105" s="7"/>
+    </row>
+    <row r="106" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="9"/>
       <c r="B106" s="5"/>
       <c r="C106" s="12"/>
       <c r="D106" s="12"/>
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="17"/>
-      <c r="I106" s="7"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="17"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -3342,17 +3488,18 @@
       <c r="T106" s="7"/>
       <c r="U106" s="7"/>
       <c r="V106" s="7"/>
-    </row>
-    <row r="107" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W106" s="7"/>
+    </row>
+    <row r="107" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="9"/>
       <c r="B107" s="5"/>
       <c r="C107" s="12"/>
       <c r="D107" s="12"/>
       <c r="E107" s="12"/>
       <c r="F107" s="12"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="17"/>
-      <c r="I107" s="7"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="17"/>
       <c r="J107" s="7"/>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -3366,17 +3513,18 @@
       <c r="T107" s="7"/>
       <c r="U107" s="7"/>
       <c r="V107" s="7"/>
-    </row>
-    <row r="108" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W107" s="7"/>
+    </row>
+    <row r="108" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="9"/>
       <c r="B108" s="5"/>
       <c r="C108" s="12"/>
       <c r="D108" s="12"/>
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="17"/>
-      <c r="I108" s="7"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="17"/>
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -3390,17 +3538,18 @@
       <c r="T108" s="7"/>
       <c r="U108" s="7"/>
       <c r="V108" s="7"/>
-    </row>
-    <row r="109" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W108" s="7"/>
+    </row>
+    <row r="109" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="9"/>
       <c r="B109" s="5"/>
       <c r="C109" s="12"/>
       <c r="D109" s="12"/>
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="17"/>
-      <c r="I109" s="7"/>
+      <c r="G109" s="12"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="17"/>
       <c r="J109" s="7"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -3414,17 +3563,18 @@
       <c r="T109" s="7"/>
       <c r="U109" s="7"/>
       <c r="V109" s="7"/>
-    </row>
-    <row r="110" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W109" s="7"/>
+    </row>
+    <row r="110" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="9"/>
       <c r="B110" s="5"/>
       <c r="C110" s="12"/>
       <c r="D110" s="12"/>
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="17"/>
-      <c r="I110" s="7"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="17"/>
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -3438,17 +3588,18 @@
       <c r="T110" s="7"/>
       <c r="U110" s="7"/>
       <c r="V110" s="7"/>
-    </row>
-    <row r="111" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W110" s="7"/>
+    </row>
+    <row r="111" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="9"/>
       <c r="B111" s="5"/>
       <c r="C111" s="12"/>
       <c r="D111" s="12"/>
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="17"/>
-      <c r="I111" s="7"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="17"/>
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -3462,17 +3613,18 @@
       <c r="T111" s="7"/>
       <c r="U111" s="7"/>
       <c r="V111" s="7"/>
-    </row>
-    <row r="112" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W111" s="7"/>
+    </row>
+    <row r="112" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="9"/>
       <c r="B112" s="5"/>
       <c r="C112" s="12"/>
       <c r="D112" s="12"/>
       <c r="E112" s="12"/>
       <c r="F112" s="12"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="17"/>
-      <c r="I112" s="7"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="17"/>
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -3486,17 +3638,18 @@
       <c r="T112" s="7"/>
       <c r="U112" s="7"/>
       <c r="V112" s="7"/>
-    </row>
-    <row r="113" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W112" s="7"/>
+    </row>
+    <row r="113" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="9"/>
       <c r="B113" s="5"/>
       <c r="C113" s="12"/>
       <c r="D113" s="12"/>
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="17"/>
-      <c r="I113" s="7"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="17"/>
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -3510,17 +3663,18 @@
       <c r="T113" s="7"/>
       <c r="U113" s="7"/>
       <c r="V113" s="7"/>
-    </row>
-    <row r="114" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W113" s="7"/>
+    </row>
+    <row r="114" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="9"/>
       <c r="B114" s="5"/>
       <c r="C114" s="12"/>
       <c r="D114" s="12"/>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="17"/>
-      <c r="I114" s="7"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="17"/>
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -3534,17 +3688,18 @@
       <c r="T114" s="7"/>
       <c r="U114" s="7"/>
       <c r="V114" s="7"/>
-    </row>
-    <row r="115" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W114" s="7"/>
+    </row>
+    <row r="115" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="9"/>
       <c r="B115" s="5"/>
       <c r="C115" s="12"/>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="17"/>
-      <c r="I115" s="7"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="17"/>
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -3558,17 +3713,18 @@
       <c r="T115" s="7"/>
       <c r="U115" s="7"/>
       <c r="V115" s="7"/>
-    </row>
-    <row r="116" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W115" s="7"/>
+    </row>
+    <row r="116" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="9"/>
       <c r="B116" s="5"/>
       <c r="C116" s="12"/>
       <c r="D116" s="12"/>
       <c r="E116" s="12"/>
       <c r="F116" s="12"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="17"/>
-      <c r="I116" s="7"/>
+      <c r="G116" s="12"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="17"/>
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -3582,17 +3738,18 @@
       <c r="T116" s="7"/>
       <c r="U116" s="7"/>
       <c r="V116" s="7"/>
-    </row>
-    <row r="117" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W116" s="7"/>
+    </row>
+    <row r="117" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="9"/>
       <c r="B117" s="5"/>
       <c r="C117" s="12"/>
       <c r="D117" s="12"/>
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="17"/>
-      <c r="I117" s="7"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="17"/>
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -3606,17 +3763,18 @@
       <c r="T117" s="7"/>
       <c r="U117" s="7"/>
       <c r="V117" s="7"/>
-    </row>
-    <row r="118" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W117" s="7"/>
+    </row>
+    <row r="118" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="9"/>
       <c r="B118" s="5"/>
       <c r="C118" s="12"/>
       <c r="D118" s="12"/>
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="17"/>
-      <c r="I118" s="7"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="17"/>
       <c r="J118" s="7"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -3630,17 +3788,18 @@
       <c r="T118" s="7"/>
       <c r="U118" s="7"/>
       <c r="V118" s="7"/>
-    </row>
-    <row r="119" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W118" s="7"/>
+    </row>
+    <row r="119" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="9"/>
       <c r="B119" s="5"/>
       <c r="C119" s="12"/>
       <c r="D119" s="12"/>
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
-      <c r="G119" s="7"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="7"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="17"/>
       <c r="J119" s="7"/>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -3654,17 +3813,18 @@
       <c r="T119" s="7"/>
       <c r="U119" s="7"/>
       <c r="V119" s="7"/>
-    </row>
-    <row r="120" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W119" s="7"/>
+    </row>
+    <row r="120" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="9"/>
       <c r="B120" s="5"/>
       <c r="C120" s="12"/>
       <c r="D120" s="12"/>
       <c r="E120" s="12"/>
       <c r="F120" s="12"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="17"/>
-      <c r="I120" s="7"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="17"/>
       <c r="J120" s="7"/>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -3678,17 +3838,18 @@
       <c r="T120" s="7"/>
       <c r="U120" s="7"/>
       <c r="V120" s="7"/>
-    </row>
-    <row r="121" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W120" s="7"/>
+    </row>
+    <row r="121" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="9"/>
       <c r="B121" s="5"/>
       <c r="C121" s="12"/>
       <c r="D121" s="12"/>
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="17"/>
-      <c r="I121" s="7"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="17"/>
       <c r="J121" s="7"/>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -3702,17 +3863,18 @@
       <c r="T121" s="7"/>
       <c r="U121" s="7"/>
       <c r="V121" s="7"/>
-    </row>
-    <row r="122" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W121" s="7"/>
+    </row>
+    <row r="122" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="9"/>
       <c r="B122" s="5"/>
       <c r="C122" s="12"/>
       <c r="D122" s="12"/>
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="17"/>
-      <c r="I122" s="7"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="17"/>
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -3726,17 +3888,18 @@
       <c r="T122" s="7"/>
       <c r="U122" s="7"/>
       <c r="V122" s="7"/>
-    </row>
-    <row r="123" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W122" s="7"/>
+    </row>
+    <row r="123" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="9"/>
       <c r="B123" s="5"/>
       <c r="C123" s="12"/>
       <c r="D123" s="12"/>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="17"/>
-      <c r="I123" s="7"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="17"/>
       <c r="J123" s="7"/>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -3750,17 +3913,18 @@
       <c r="T123" s="7"/>
       <c r="U123" s="7"/>
       <c r="V123" s="7"/>
-    </row>
-    <row r="124" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W123" s="7"/>
+    </row>
+    <row r="124" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="9"/>
       <c r="B124" s="5"/>
       <c r="C124" s="12"/>
       <c r="D124" s="12"/>
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="17"/>
-      <c r="I124" s="7"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="7"/>
+      <c r="I124" s="17"/>
       <c r="J124" s="7"/>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -3774,17 +3938,18 @@
       <c r="T124" s="7"/>
       <c r="U124" s="7"/>
       <c r="V124" s="7"/>
-    </row>
-    <row r="125" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W124" s="7"/>
+    </row>
+    <row r="125" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="9"/>
       <c r="B125" s="5"/>
       <c r="C125" s="12"/>
       <c r="D125" s="12"/>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="17"/>
-      <c r="I125" s="7"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="17"/>
       <c r="J125" s="7"/>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -3798,17 +3963,18 @@
       <c r="T125" s="7"/>
       <c r="U125" s="7"/>
       <c r="V125" s="7"/>
-    </row>
-    <row r="126" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W125" s="7"/>
+    </row>
+    <row r="126" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="9"/>
       <c r="B126" s="5"/>
       <c r="C126" s="12"/>
       <c r="D126" s="12"/>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="17"/>
-      <c r="I126" s="7"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="17"/>
       <c r="J126" s="7"/>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -3822,17 +3988,18 @@
       <c r="T126" s="7"/>
       <c r="U126" s="7"/>
       <c r="V126" s="7"/>
-    </row>
-    <row r="127" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W126" s="7"/>
+    </row>
+    <row r="127" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="9"/>
       <c r="B127" s="5"/>
       <c r="C127" s="12"/>
       <c r="D127" s="12"/>
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
-      <c r="G127" s="7"/>
-      <c r="H127" s="17"/>
-      <c r="I127" s="7"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="7"/>
+      <c r="I127" s="17"/>
       <c r="J127" s="7"/>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -3846,17 +4013,18 @@
       <c r="T127" s="7"/>
       <c r="U127" s="7"/>
       <c r="V127" s="7"/>
-    </row>
-    <row r="128" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W127" s="7"/>
+    </row>
+    <row r="128" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="9"/>
       <c r="B128" s="5"/>
       <c r="C128" s="12"/>
       <c r="D128" s="12"/>
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="17"/>
-      <c r="I128" s="7"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="7"/>
+      <c r="I128" s="17"/>
       <c r="J128" s="7"/>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -3870,17 +4038,18 @@
       <c r="T128" s="7"/>
       <c r="U128" s="7"/>
       <c r="V128" s="7"/>
-    </row>
-    <row r="129" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W128" s="7"/>
+    </row>
+    <row r="129" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="9"/>
       <c r="B129" s="5"/>
       <c r="C129" s="12"/>
       <c r="D129" s="12"/>
       <c r="E129" s="12"/>
       <c r="F129" s="12"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="17"/>
-      <c r="I129" s="7"/>
+      <c r="G129" s="12"/>
+      <c r="H129" s="7"/>
+      <c r="I129" s="17"/>
       <c r="J129" s="7"/>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -3894,17 +4063,18 @@
       <c r="T129" s="7"/>
       <c r="U129" s="7"/>
       <c r="V129" s="7"/>
-    </row>
-    <row r="130" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W129" s="7"/>
+    </row>
+    <row r="130" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="9"/>
       <c r="B130" s="5"/>
       <c r="C130" s="12"/>
       <c r="D130" s="12"/>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="17"/>
-      <c r="I130" s="7"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="7"/>
+      <c r="I130" s="17"/>
       <c r="J130" s="7"/>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -3918,17 +4088,18 @@
       <c r="T130" s="7"/>
       <c r="U130" s="7"/>
       <c r="V130" s="7"/>
-    </row>
-    <row r="131" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W130" s="7"/>
+    </row>
+    <row r="131" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="9"/>
       <c r="B131" s="5"/>
       <c r="C131" s="12"/>
       <c r="D131" s="12"/>
       <c r="E131" s="12"/>
       <c r="F131" s="12"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="17"/>
-      <c r="I131" s="7"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="7"/>
+      <c r="I131" s="17"/>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -3942,17 +4113,18 @@
       <c r="T131" s="7"/>
       <c r="U131" s="7"/>
       <c r="V131" s="7"/>
-    </row>
-    <row r="132" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W131" s="7"/>
+    </row>
+    <row r="132" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="9"/>
       <c r="B132" s="5"/>
       <c r="C132" s="12"/>
       <c r="D132" s="12"/>
       <c r="E132" s="12"/>
       <c r="F132" s="12"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="17"/>
-      <c r="I132" s="7"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="17"/>
       <c r="J132" s="7"/>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -3966,17 +4138,18 @@
       <c r="T132" s="7"/>
       <c r="U132" s="7"/>
       <c r="V132" s="7"/>
-    </row>
-    <row r="133" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W132" s="7"/>
+    </row>
+    <row r="133" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="9"/>
       <c r="B133" s="5"/>
       <c r="C133" s="12"/>
       <c r="D133" s="12"/>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="17"/>
-      <c r="I133" s="7"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="7"/>
+      <c r="I133" s="17"/>
       <c r="J133" s="7"/>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -3990,17 +4163,18 @@
       <c r="T133" s="7"/>
       <c r="U133" s="7"/>
       <c r="V133" s="7"/>
-    </row>
-    <row r="134" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W133" s="7"/>
+    </row>
+    <row r="134" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="9"/>
       <c r="B134" s="5"/>
       <c r="C134" s="12"/>
       <c r="D134" s="12"/>
       <c r="E134" s="12"/>
       <c r="F134" s="12"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="17"/>
-      <c r="I134" s="7"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="17"/>
       <c r="J134" s="7"/>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -4014,17 +4188,18 @@
       <c r="T134" s="7"/>
       <c r="U134" s="7"/>
       <c r="V134" s="7"/>
-    </row>
-    <row r="135" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W134" s="7"/>
+    </row>
+    <row r="135" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="9"/>
       <c r="B135" s="5"/>
       <c r="C135" s="12"/>
       <c r="D135" s="12"/>
       <c r="E135" s="12"/>
       <c r="F135" s="12"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="17"/>
-      <c r="I135" s="7"/>
+      <c r="G135" s="12"/>
+      <c r="H135" s="7"/>
+      <c r="I135" s="17"/>
       <c r="J135" s="7"/>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -4038,17 +4213,18 @@
       <c r="T135" s="7"/>
       <c r="U135" s="7"/>
       <c r="V135" s="7"/>
-    </row>
-    <row r="136" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W135" s="7"/>
+    </row>
+    <row r="136" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="9"/>
       <c r="B136" s="5"/>
       <c r="C136" s="12"/>
       <c r="D136" s="12"/>
       <c r="E136" s="12"/>
       <c r="F136" s="12"/>
-      <c r="G136" s="7"/>
-      <c r="H136" s="17"/>
-      <c r="I136" s="7"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="17"/>
       <c r="J136" s="7"/>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -4062,17 +4238,18 @@
       <c r="T136" s="7"/>
       <c r="U136" s="7"/>
       <c r="V136" s="7"/>
-    </row>
-    <row r="137" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W136" s="7"/>
+    </row>
+    <row r="137" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="9"/>
       <c r="B137" s="5"/>
       <c r="C137" s="12"/>
       <c r="D137" s="12"/>
       <c r="E137" s="12"/>
       <c r="F137" s="12"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="17"/>
-      <c r="I137" s="7"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="17"/>
       <c r="J137" s="7"/>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -4086,17 +4263,18 @@
       <c r="T137" s="7"/>
       <c r="U137" s="7"/>
       <c r="V137" s="7"/>
-    </row>
-    <row r="138" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W137" s="7"/>
+    </row>
+    <row r="138" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="9"/>
       <c r="B138" s="5"/>
       <c r="C138" s="12"/>
       <c r="D138" s="12"/>
       <c r="E138" s="12"/>
       <c r="F138" s="12"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="17"/>
-      <c r="I138" s="7"/>
+      <c r="G138" s="12"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="17"/>
       <c r="J138" s="7"/>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -4110,17 +4288,18 @@
       <c r="T138" s="7"/>
       <c r="U138" s="7"/>
       <c r="V138" s="7"/>
-    </row>
-    <row r="139" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W138" s="7"/>
+    </row>
+    <row r="139" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="9"/>
       <c r="B139" s="5"/>
       <c r="C139" s="12"/>
       <c r="D139" s="12"/>
       <c r="E139" s="12"/>
       <c r="F139" s="12"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="17"/>
-      <c r="I139" s="7"/>
+      <c r="G139" s="12"/>
+      <c r="H139" s="7"/>
+      <c r="I139" s="17"/>
       <c r="J139" s="7"/>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -4134,17 +4313,18 @@
       <c r="T139" s="7"/>
       <c r="U139" s="7"/>
       <c r="V139" s="7"/>
-    </row>
-    <row r="140" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W139" s="7"/>
+    </row>
+    <row r="140" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="9"/>
       <c r="B140" s="5"/>
       <c r="C140" s="12"/>
       <c r="D140" s="12"/>
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="17"/>
-      <c r="I140" s="7"/>
+      <c r="G140" s="12"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="17"/>
       <c r="J140" s="7"/>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -4158,17 +4338,18 @@
       <c r="T140" s="7"/>
       <c r="U140" s="7"/>
       <c r="V140" s="7"/>
-    </row>
-    <row r="141" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W140" s="7"/>
+    </row>
+    <row r="141" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="9"/>
       <c r="B141" s="5"/>
       <c r="C141" s="12"/>
       <c r="D141" s="12"/>
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
-      <c r="G141" s="7"/>
-      <c r="H141" s="17"/>
-      <c r="I141" s="7"/>
+      <c r="G141" s="12"/>
+      <c r="H141" s="7"/>
+      <c r="I141" s="17"/>
       <c r="J141" s="7"/>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -4182,17 +4363,18 @@
       <c r="T141" s="7"/>
       <c r="U141" s="7"/>
       <c r="V141" s="7"/>
-    </row>
-    <row r="142" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W141" s="7"/>
+    </row>
+    <row r="142" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="9"/>
       <c r="B142" s="5"/>
       <c r="C142" s="12"/>
       <c r="D142" s="12"/>
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="17"/>
-      <c r="I142" s="7"/>
+      <c r="G142" s="12"/>
+      <c r="H142" s="7"/>
+      <c r="I142" s="17"/>
       <c r="J142" s="7"/>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -4206,17 +4388,18 @@
       <c r="T142" s="7"/>
       <c r="U142" s="7"/>
       <c r="V142" s="7"/>
-    </row>
-    <row r="143" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W142" s="7"/>
+    </row>
+    <row r="143" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="9"/>
       <c r="B143" s="5"/>
       <c r="C143" s="12"/>
       <c r="D143" s="12"/>
       <c r="E143" s="12"/>
       <c r="F143" s="12"/>
-      <c r="G143" s="7"/>
-      <c r="H143" s="17"/>
-      <c r="I143" s="7"/>
+      <c r="G143" s="12"/>
+      <c r="H143" s="7"/>
+      <c r="I143" s="17"/>
       <c r="J143" s="7"/>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -4230,17 +4413,18 @@
       <c r="T143" s="7"/>
       <c r="U143" s="7"/>
       <c r="V143" s="7"/>
-    </row>
-    <row r="144" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W143" s="7"/>
+    </row>
+    <row r="144" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="9"/>
       <c r="B144" s="5"/>
       <c r="C144" s="12"/>
       <c r="D144" s="12"/>
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="17"/>
-      <c r="I144" s="7"/>
+      <c r="G144" s="12"/>
+      <c r="H144" s="7"/>
+      <c r="I144" s="17"/>
       <c r="J144" s="7"/>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -4254,17 +4438,18 @@
       <c r="T144" s="7"/>
       <c r="U144" s="7"/>
       <c r="V144" s="7"/>
-    </row>
-    <row r="145" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W144" s="7"/>
+    </row>
+    <row r="145" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="9"/>
       <c r="B145" s="5"/>
       <c r="C145" s="12"/>
       <c r="D145" s="12"/>
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="17"/>
-      <c r="I145" s="7"/>
+      <c r="G145" s="12"/>
+      <c r="H145" s="7"/>
+      <c r="I145" s="17"/>
       <c r="J145" s="7"/>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -4278,17 +4463,18 @@
       <c r="T145" s="7"/>
       <c r="U145" s="7"/>
       <c r="V145" s="7"/>
-    </row>
-    <row r="146" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W145" s="7"/>
+    </row>
+    <row r="146" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="9"/>
       <c r="B146" s="5"/>
       <c r="C146" s="12"/>
       <c r="D146" s="12"/>
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="17"/>
-      <c r="I146" s="7"/>
+      <c r="G146" s="12"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="17"/>
       <c r="J146" s="7"/>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -4302,17 +4488,18 @@
       <c r="T146" s="7"/>
       <c r="U146" s="7"/>
       <c r="V146" s="7"/>
-    </row>
-    <row r="147" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W146" s="7"/>
+    </row>
+    <row r="147" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="9"/>
       <c r="B147" s="5"/>
       <c r="C147" s="12"/>
       <c r="D147" s="12"/>
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="17"/>
-      <c r="I147" s="7"/>
+      <c r="G147" s="12"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="17"/>
       <c r="J147" s="7"/>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -4326,17 +4513,18 @@
       <c r="T147" s="7"/>
       <c r="U147" s="7"/>
       <c r="V147" s="7"/>
-    </row>
-    <row r="148" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W147" s="7"/>
+    </row>
+    <row r="148" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="9"/>
       <c r="B148" s="5"/>
       <c r="C148" s="12"/>
       <c r="D148" s="12"/>
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
-      <c r="G148" s="7"/>
-      <c r="H148" s="17"/>
-      <c r="I148" s="7"/>
+      <c r="G148" s="12"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="17"/>
       <c r="J148" s="7"/>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -4350,17 +4538,18 @@
       <c r="T148" s="7"/>
       <c r="U148" s="7"/>
       <c r="V148" s="7"/>
-    </row>
-    <row r="149" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W148" s="7"/>
+    </row>
+    <row r="149" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="9"/>
       <c r="B149" s="5"/>
       <c r="C149" s="12"/>
       <c r="D149" s="12"/>
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="17"/>
-      <c r="I149" s="7"/>
+      <c r="G149" s="12"/>
+      <c r="H149" s="7"/>
+      <c r="I149" s="17"/>
       <c r="J149" s="7"/>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -4374,17 +4563,18 @@
       <c r="T149" s="7"/>
       <c r="U149" s="7"/>
       <c r="V149" s="7"/>
-    </row>
-    <row r="150" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W149" s="7"/>
+    </row>
+    <row r="150" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="9"/>
       <c r="B150" s="5"/>
       <c r="C150" s="12"/>
       <c r="D150" s="12"/>
       <c r="E150" s="12"/>
       <c r="F150" s="12"/>
-      <c r="G150" s="7"/>
-      <c r="H150" s="17"/>
-      <c r="I150" s="7"/>
+      <c r="G150" s="12"/>
+      <c r="H150" s="7"/>
+      <c r="I150" s="17"/>
       <c r="J150" s="7"/>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -4398,17 +4588,18 @@
       <c r="T150" s="7"/>
       <c r="U150" s="7"/>
       <c r="V150" s="7"/>
-    </row>
-    <row r="151" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W150" s="7"/>
+    </row>
+    <row r="151" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="9"/>
       <c r="B151" s="5"/>
       <c r="C151" s="12"/>
       <c r="D151" s="12"/>
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="17"/>
-      <c r="I151" s="7"/>
+      <c r="G151" s="12"/>
+      <c r="H151" s="7"/>
+      <c r="I151" s="17"/>
       <c r="J151" s="7"/>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -4422,17 +4613,18 @@
       <c r="T151" s="7"/>
       <c r="U151" s="7"/>
       <c r="V151" s="7"/>
-    </row>
-    <row r="152" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W151" s="7"/>
+    </row>
+    <row r="152" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="9"/>
       <c r="B152" s="5"/>
       <c r="C152" s="12"/>
       <c r="D152" s="12"/>
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="17"/>
-      <c r="I152" s="7"/>
+      <c r="G152" s="12"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="17"/>
       <c r="J152" s="7"/>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -4446,17 +4638,18 @@
       <c r="T152" s="7"/>
       <c r="U152" s="7"/>
       <c r="V152" s="7"/>
-    </row>
-    <row r="153" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W152" s="7"/>
+    </row>
+    <row r="153" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="9"/>
       <c r="B153" s="5"/>
       <c r="C153" s="12"/>
       <c r="D153" s="12"/>
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="17"/>
-      <c r="I153" s="7"/>
+      <c r="G153" s="12"/>
+      <c r="H153" s="7"/>
+      <c r="I153" s="17"/>
       <c r="J153" s="7"/>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -4470,17 +4663,18 @@
       <c r="T153" s="7"/>
       <c r="U153" s="7"/>
       <c r="V153" s="7"/>
-    </row>
-    <row r="154" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W153" s="7"/>
+    </row>
+    <row r="154" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="9"/>
       <c r="B154" s="5"/>
       <c r="C154" s="12"/>
       <c r="D154" s="12"/>
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
-      <c r="G154" s="7"/>
-      <c r="H154" s="17"/>
-      <c r="I154" s="7"/>
+      <c r="G154" s="12"/>
+      <c r="H154" s="7"/>
+      <c r="I154" s="17"/>
       <c r="J154" s="7"/>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -4494,17 +4688,18 @@
       <c r="T154" s="7"/>
       <c r="U154" s="7"/>
       <c r="V154" s="7"/>
-    </row>
-    <row r="155" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W154" s="7"/>
+    </row>
+    <row r="155" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="9"/>
       <c r="B155" s="5"/>
       <c r="C155" s="12"/>
       <c r="D155" s="12"/>
       <c r="E155" s="12"/>
       <c r="F155" s="12"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="17"/>
-      <c r="I155" s="7"/>
+      <c r="G155" s="12"/>
+      <c r="H155" s="7"/>
+      <c r="I155" s="17"/>
       <c r="J155" s="7"/>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -4518,17 +4713,18 @@
       <c r="T155" s="7"/>
       <c r="U155" s="7"/>
       <c r="V155" s="7"/>
-    </row>
-    <row r="156" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W155" s="7"/>
+    </row>
+    <row r="156" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="9"/>
       <c r="B156" s="5"/>
       <c r="C156" s="12"/>
       <c r="D156" s="12"/>
       <c r="E156" s="12"/>
       <c r="F156" s="12"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="17"/>
-      <c r="I156" s="7"/>
+      <c r="G156" s="12"/>
+      <c r="H156" s="7"/>
+      <c r="I156" s="17"/>
       <c r="J156" s="7"/>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -4542,17 +4738,18 @@
       <c r="T156" s="7"/>
       <c r="U156" s="7"/>
       <c r="V156" s="7"/>
-    </row>
-    <row r="157" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W156" s="7"/>
+    </row>
+    <row r="157" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="9"/>
       <c r="B157" s="5"/>
       <c r="C157" s="12"/>
       <c r="D157" s="12"/>
       <c r="E157" s="12"/>
       <c r="F157" s="12"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="17"/>
-      <c r="I157" s="7"/>
+      <c r="G157" s="12"/>
+      <c r="H157" s="7"/>
+      <c r="I157" s="17"/>
       <c r="J157" s="7"/>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -4566,17 +4763,18 @@
       <c r="T157" s="7"/>
       <c r="U157" s="7"/>
       <c r="V157" s="7"/>
-    </row>
-    <row r="158" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W157" s="7"/>
+    </row>
+    <row r="158" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="9"/>
       <c r="B158" s="5"/>
       <c r="C158" s="12"/>
       <c r="D158" s="12"/>
       <c r="E158" s="12"/>
       <c r="F158" s="12"/>
-      <c r="G158" s="7"/>
-      <c r="H158" s="17"/>
-      <c r="I158" s="7"/>
+      <c r="G158" s="12"/>
+      <c r="H158" s="7"/>
+      <c r="I158" s="17"/>
       <c r="J158" s="7"/>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -4590,17 +4788,18 @@
       <c r="T158" s="7"/>
       <c r="U158" s="7"/>
       <c r="V158" s="7"/>
-    </row>
-    <row r="159" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W158" s="7"/>
+    </row>
+    <row r="159" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="9"/>
       <c r="B159" s="5"/>
       <c r="C159" s="12"/>
       <c r="D159" s="12"/>
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
-      <c r="G159" s="7"/>
-      <c r="H159" s="17"/>
-      <c r="I159" s="7"/>
+      <c r="G159" s="12"/>
+      <c r="H159" s="7"/>
+      <c r="I159" s="17"/>
       <c r="J159" s="7"/>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -4614,17 +4813,18 @@
       <c r="T159" s="7"/>
       <c r="U159" s="7"/>
       <c r="V159" s="7"/>
-    </row>
-    <row r="160" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W159" s="7"/>
+    </row>
+    <row r="160" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="9"/>
       <c r="B160" s="5"/>
       <c r="C160" s="12"/>
       <c r="D160" s="12"/>
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="17"/>
-      <c r="I160" s="7"/>
+      <c r="G160" s="12"/>
+      <c r="H160" s="7"/>
+      <c r="I160" s="17"/>
       <c r="J160" s="7"/>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -4638,17 +4838,18 @@
       <c r="T160" s="7"/>
       <c r="U160" s="7"/>
       <c r="V160" s="7"/>
-    </row>
-    <row r="161" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W160" s="7"/>
+    </row>
+    <row r="161" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="9"/>
       <c r="B161" s="5"/>
       <c r="C161" s="12"/>
       <c r="D161" s="12"/>
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
-      <c r="G161" s="7"/>
-      <c r="H161" s="17"/>
-      <c r="I161" s="7"/>
+      <c r="G161" s="12"/>
+      <c r="H161" s="7"/>
+      <c r="I161" s="17"/>
       <c r="J161" s="7"/>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -4662,17 +4863,18 @@
       <c r="T161" s="7"/>
       <c r="U161" s="7"/>
       <c r="V161" s="7"/>
-    </row>
-    <row r="162" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W161" s="7"/>
+    </row>
+    <row r="162" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="9"/>
       <c r="B162" s="5"/>
       <c r="C162" s="12"/>
       <c r="D162" s="12"/>
       <c r="E162" s="12"/>
       <c r="F162" s="12"/>
-      <c r="G162" s="7"/>
-      <c r="H162" s="17"/>
-      <c r="I162" s="7"/>
+      <c r="G162" s="12"/>
+      <c r="H162" s="7"/>
+      <c r="I162" s="17"/>
       <c r="J162" s="7"/>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -4686,17 +4888,18 @@
       <c r="T162" s="7"/>
       <c r="U162" s="7"/>
       <c r="V162" s="7"/>
-    </row>
-    <row r="163" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W162" s="7"/>
+    </row>
+    <row r="163" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="9"/>
       <c r="B163" s="5"/>
       <c r="C163" s="12"/>
       <c r="D163" s="12"/>
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
-      <c r="G163" s="7"/>
-      <c r="H163" s="17"/>
-      <c r="I163" s="7"/>
+      <c r="G163" s="12"/>
+      <c r="H163" s="7"/>
+      <c r="I163" s="17"/>
       <c r="J163" s="7"/>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -4710,17 +4913,18 @@
       <c r="T163" s="7"/>
       <c r="U163" s="7"/>
       <c r="V163" s="7"/>
-    </row>
-    <row r="164" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W163" s="7"/>
+    </row>
+    <row r="164" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="9"/>
       <c r="B164" s="5"/>
       <c r="C164" s="12"/>
       <c r="D164" s="12"/>
       <c r="E164" s="12"/>
       <c r="F164" s="12"/>
-      <c r="G164" s="7"/>
-      <c r="H164" s="17"/>
-      <c r="I164" s="7"/>
+      <c r="G164" s="12"/>
+      <c r="H164" s="7"/>
+      <c r="I164" s="17"/>
       <c r="J164" s="7"/>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -4734,17 +4938,18 @@
       <c r="T164" s="7"/>
       <c r="U164" s="7"/>
       <c r="V164" s="7"/>
-    </row>
-    <row r="165" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W164" s="7"/>
+    </row>
+    <row r="165" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="9"/>
       <c r="B165" s="5"/>
       <c r="C165" s="12"/>
       <c r="D165" s="12"/>
       <c r="E165" s="12"/>
       <c r="F165" s="12"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="17"/>
-      <c r="I165" s="7"/>
+      <c r="G165" s="12"/>
+      <c r="H165" s="7"/>
+      <c r="I165" s="17"/>
       <c r="J165" s="7"/>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -4758,17 +4963,18 @@
       <c r="T165" s="7"/>
       <c r="U165" s="7"/>
       <c r="V165" s="7"/>
-    </row>
-    <row r="166" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W165" s="7"/>
+    </row>
+    <row r="166" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="9"/>
       <c r="B166" s="5"/>
       <c r="C166" s="12"/>
       <c r="D166" s="12"/>
       <c r="E166" s="12"/>
       <c r="F166" s="12"/>
-      <c r="G166" s="7"/>
-      <c r="H166" s="17"/>
-      <c r="I166" s="7"/>
+      <c r="G166" s="12"/>
+      <c r="H166" s="7"/>
+      <c r="I166" s="17"/>
       <c r="J166" s="7"/>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -4782,17 +4988,18 @@
       <c r="T166" s="7"/>
       <c r="U166" s="7"/>
       <c r="V166" s="7"/>
-    </row>
-    <row r="167" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W166" s="7"/>
+    </row>
+    <row r="167" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="9"/>
       <c r="B167" s="5"/>
       <c r="C167" s="12"/>
       <c r="D167" s="12"/>
       <c r="E167" s="12"/>
       <c r="F167" s="12"/>
-      <c r="G167" s="7"/>
-      <c r="H167" s="17"/>
-      <c r="I167" s="7"/>
+      <c r="G167" s="12"/>
+      <c r="H167" s="7"/>
+      <c r="I167" s="17"/>
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -4806,17 +5013,18 @@
       <c r="T167" s="7"/>
       <c r="U167" s="7"/>
       <c r="V167" s="7"/>
-    </row>
-    <row r="168" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W167" s="7"/>
+    </row>
+    <row r="168" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="9"/>
       <c r="B168" s="5"/>
       <c r="C168" s="12"/>
       <c r="D168" s="12"/>
       <c r="E168" s="12"/>
       <c r="F168" s="12"/>
-      <c r="G168" s="7"/>
-      <c r="H168" s="17"/>
-      <c r="I168" s="7"/>
+      <c r="G168" s="12"/>
+      <c r="H168" s="7"/>
+      <c r="I168" s="17"/>
       <c r="J168" s="7"/>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -4830,17 +5038,18 @@
       <c r="T168" s="7"/>
       <c r="U168" s="7"/>
       <c r="V168" s="7"/>
-    </row>
-    <row r="169" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W168" s="7"/>
+    </row>
+    <row r="169" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="9"/>
       <c r="B169" s="5"/>
       <c r="C169" s="12"/>
       <c r="D169" s="12"/>
       <c r="E169" s="12"/>
       <c r="F169" s="12"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="17"/>
-      <c r="I169" s="7"/>
+      <c r="G169" s="12"/>
+      <c r="H169" s="7"/>
+      <c r="I169" s="17"/>
       <c r="J169" s="7"/>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -4854,17 +5063,18 @@
       <c r="T169" s="7"/>
       <c r="U169" s="7"/>
       <c r="V169" s="7"/>
-    </row>
-    <row r="170" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W169" s="7"/>
+    </row>
+    <row r="170" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="9"/>
       <c r="B170" s="5"/>
       <c r="C170" s="12"/>
       <c r="D170" s="12"/>
       <c r="E170" s="12"/>
       <c r="F170" s="12"/>
-      <c r="G170" s="7"/>
-      <c r="H170" s="17"/>
-      <c r="I170" s="7"/>
+      <c r="G170" s="12"/>
+      <c r="H170" s="7"/>
+      <c r="I170" s="17"/>
       <c r="J170" s="7"/>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -4878,17 +5088,18 @@
       <c r="T170" s="7"/>
       <c r="U170" s="7"/>
       <c r="V170" s="7"/>
-    </row>
-    <row r="171" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W170" s="7"/>
+    </row>
+    <row r="171" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="9"/>
       <c r="B171" s="5"/>
       <c r="C171" s="12"/>
       <c r="D171" s="12"/>
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
-      <c r="G171" s="7"/>
-      <c r="H171" s="17"/>
-      <c r="I171" s="7"/>
+      <c r="G171" s="12"/>
+      <c r="H171" s="7"/>
+      <c r="I171" s="17"/>
       <c r="J171" s="7"/>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -4902,17 +5113,18 @@
       <c r="T171" s="7"/>
       <c r="U171" s="7"/>
       <c r="V171" s="7"/>
-    </row>
-    <row r="172" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W171" s="7"/>
+    </row>
+    <row r="172" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="9"/>
       <c r="B172" s="5"/>
       <c r="C172" s="12"/>
       <c r="D172" s="12"/>
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
-      <c r="G172" s="7"/>
-      <c r="H172" s="17"/>
-      <c r="I172" s="7"/>
+      <c r="G172" s="12"/>
+      <c r="H172" s="7"/>
+      <c r="I172" s="17"/>
       <c r="J172" s="7"/>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -4926,17 +5138,18 @@
       <c r="T172" s="7"/>
       <c r="U172" s="7"/>
       <c r="V172" s="7"/>
-    </row>
-    <row r="173" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W172" s="7"/>
+    </row>
+    <row r="173" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="9"/>
       <c r="B173" s="5"/>
       <c r="C173" s="12"/>
       <c r="D173" s="12"/>
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
-      <c r="G173" s="7"/>
-      <c r="H173" s="17"/>
-      <c r="I173" s="7"/>
+      <c r="G173" s="12"/>
+      <c r="H173" s="7"/>
+      <c r="I173" s="17"/>
       <c r="J173" s="7"/>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -4950,17 +5163,18 @@
       <c r="T173" s="7"/>
       <c r="U173" s="7"/>
       <c r="V173" s="7"/>
-    </row>
-    <row r="174" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W173" s="7"/>
+    </row>
+    <row r="174" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="9"/>
       <c r="B174" s="5"/>
       <c r="C174" s="12"/>
       <c r="D174" s="12"/>
       <c r="E174" s="12"/>
       <c r="F174" s="12"/>
-      <c r="G174" s="7"/>
-      <c r="H174" s="17"/>
-      <c r="I174" s="7"/>
+      <c r="G174" s="12"/>
+      <c r="H174" s="7"/>
+      <c r="I174" s="17"/>
       <c r="J174" s="7"/>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -4974,17 +5188,18 @@
       <c r="T174" s="7"/>
       <c r="U174" s="7"/>
       <c r="V174" s="7"/>
-    </row>
-    <row r="175" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W174" s="7"/>
+    </row>
+    <row r="175" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="9"/>
       <c r="B175" s="5"/>
       <c r="C175" s="12"/>
       <c r="D175" s="12"/>
       <c r="E175" s="12"/>
       <c r="F175" s="12"/>
-      <c r="G175" s="7"/>
-      <c r="H175" s="17"/>
-      <c r="I175" s="7"/>
+      <c r="G175" s="12"/>
+      <c r="H175" s="7"/>
+      <c r="I175" s="17"/>
       <c r="J175" s="7"/>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -4998,17 +5213,18 @@
       <c r="T175" s="7"/>
       <c r="U175" s="7"/>
       <c r="V175" s="7"/>
-    </row>
-    <row r="176" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W175" s="7"/>
+    </row>
+    <row r="176" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="9"/>
       <c r="B176" s="5"/>
       <c r="C176" s="12"/>
       <c r="D176" s="12"/>
       <c r="E176" s="12"/>
       <c r="F176" s="12"/>
-      <c r="G176" s="7"/>
-      <c r="H176" s="17"/>
-      <c r="I176" s="7"/>
+      <c r="G176" s="12"/>
+      <c r="H176" s="7"/>
+      <c r="I176" s="17"/>
       <c r="J176" s="7"/>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -5022,17 +5238,18 @@
       <c r="T176" s="7"/>
       <c r="U176" s="7"/>
       <c r="V176" s="7"/>
-    </row>
-    <row r="177" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W176" s="7"/>
+    </row>
+    <row r="177" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="9"/>
       <c r="B177" s="5"/>
       <c r="C177" s="12"/>
       <c r="D177" s="12"/>
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
-      <c r="G177" s="7"/>
-      <c r="H177" s="17"/>
-      <c r="I177" s="7"/>
+      <c r="G177" s="12"/>
+      <c r="H177" s="7"/>
+      <c r="I177" s="17"/>
       <c r="J177" s="7"/>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -5046,17 +5263,18 @@
       <c r="T177" s="7"/>
       <c r="U177" s="7"/>
       <c r="V177" s="7"/>
-    </row>
-    <row r="178" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W177" s="7"/>
+    </row>
+    <row r="178" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="9"/>
       <c r="B178" s="5"/>
       <c r="C178" s="12"/>
       <c r="D178" s="12"/>
       <c r="E178" s="12"/>
       <c r="F178" s="12"/>
-      <c r="G178" s="7"/>
-      <c r="H178" s="17"/>
-      <c r="I178" s="7"/>
+      <c r="G178" s="12"/>
+      <c r="H178" s="7"/>
+      <c r="I178" s="17"/>
       <c r="J178" s="7"/>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -5070,17 +5288,18 @@
       <c r="T178" s="7"/>
       <c r="U178" s="7"/>
       <c r="V178" s="7"/>
-    </row>
-    <row r="179" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W178" s="7"/>
+    </row>
+    <row r="179" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="9"/>
       <c r="B179" s="5"/>
       <c r="C179" s="12"/>
       <c r="D179" s="12"/>
       <c r="E179" s="12"/>
       <c r="F179" s="12"/>
-      <c r="G179" s="7"/>
-      <c r="H179" s="17"/>
-      <c r="I179" s="7"/>
+      <c r="G179" s="12"/>
+      <c r="H179" s="7"/>
+      <c r="I179" s="17"/>
       <c r="J179" s="7"/>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -5094,17 +5313,18 @@
       <c r="T179" s="7"/>
       <c r="U179" s="7"/>
       <c r="V179" s="7"/>
-    </row>
-    <row r="180" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W179" s="7"/>
+    </row>
+    <row r="180" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="9"/>
       <c r="B180" s="5"/>
       <c r="C180" s="12"/>
       <c r="D180" s="12"/>
       <c r="E180" s="12"/>
       <c r="F180" s="12"/>
-      <c r="G180" s="7"/>
-      <c r="H180" s="17"/>
-      <c r="I180" s="7"/>
+      <c r="G180" s="12"/>
+      <c r="H180" s="7"/>
+      <c r="I180" s="17"/>
       <c r="J180" s="7"/>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -5118,17 +5338,18 @@
       <c r="T180" s="7"/>
       <c r="U180" s="7"/>
       <c r="V180" s="7"/>
-    </row>
-    <row r="181" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W180" s="7"/>
+    </row>
+    <row r="181" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="9"/>
       <c r="B181" s="5"/>
       <c r="C181" s="12"/>
       <c r="D181" s="12"/>
       <c r="E181" s="12"/>
       <c r="F181" s="12"/>
-      <c r="G181" s="7"/>
-      <c r="H181" s="17"/>
-      <c r="I181" s="7"/>
+      <c r="G181" s="12"/>
+      <c r="H181" s="7"/>
+      <c r="I181" s="17"/>
       <c r="J181" s="7"/>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -5142,17 +5363,18 @@
       <c r="T181" s="7"/>
       <c r="U181" s="7"/>
       <c r="V181" s="7"/>
-    </row>
-    <row r="182" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W181" s="7"/>
+    </row>
+    <row r="182" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="9"/>
       <c r="B182" s="5"/>
       <c r="C182" s="12"/>
       <c r="D182" s="12"/>
       <c r="E182" s="12"/>
       <c r="F182" s="12"/>
-      <c r="G182" s="7"/>
-      <c r="H182" s="17"/>
-      <c r="I182" s="7"/>
+      <c r="G182" s="12"/>
+      <c r="H182" s="7"/>
+      <c r="I182" s="17"/>
       <c r="J182" s="7"/>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -5166,17 +5388,18 @@
       <c r="T182" s="7"/>
       <c r="U182" s="7"/>
       <c r="V182" s="7"/>
-    </row>
-    <row r="183" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W182" s="7"/>
+    </row>
+    <row r="183" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="9"/>
       <c r="B183" s="5"/>
       <c r="C183" s="12"/>
       <c r="D183" s="12"/>
       <c r="E183" s="12"/>
       <c r="F183" s="12"/>
-      <c r="G183" s="7"/>
-      <c r="H183" s="17"/>
-      <c r="I183" s="7"/>
+      <c r="G183" s="12"/>
+      <c r="H183" s="7"/>
+      <c r="I183" s="17"/>
       <c r="J183" s="7"/>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -5190,17 +5413,18 @@
       <c r="T183" s="7"/>
       <c r="U183" s="7"/>
       <c r="V183" s="7"/>
-    </row>
-    <row r="184" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W183" s="7"/>
+    </row>
+    <row r="184" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="9"/>
       <c r="B184" s="5"/>
       <c r="C184" s="12"/>
       <c r="D184" s="12"/>
       <c r="E184" s="12"/>
       <c r="F184" s="12"/>
-      <c r="G184" s="7"/>
-      <c r="H184" s="17"/>
-      <c r="I184" s="7"/>
+      <c r="G184" s="12"/>
+      <c r="H184" s="7"/>
+      <c r="I184" s="17"/>
       <c r="J184" s="7"/>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -5214,17 +5438,18 @@
       <c r="T184" s="7"/>
       <c r="U184" s="7"/>
       <c r="V184" s="7"/>
-    </row>
-    <row r="185" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W184" s="7"/>
+    </row>
+    <row r="185" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="9"/>
       <c r="B185" s="5"/>
       <c r="C185" s="12"/>
       <c r="D185" s="12"/>
       <c r="E185" s="12"/>
       <c r="F185" s="12"/>
-      <c r="G185" s="7"/>
-      <c r="H185" s="17"/>
-      <c r="I185" s="7"/>
+      <c r="G185" s="12"/>
+      <c r="H185" s="7"/>
+      <c r="I185" s="17"/>
       <c r="J185" s="7"/>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -5238,17 +5463,18 @@
       <c r="T185" s="7"/>
       <c r="U185" s="7"/>
       <c r="V185" s="7"/>
-    </row>
-    <row r="186" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W185" s="7"/>
+    </row>
+    <row r="186" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="9"/>
       <c r="B186" s="5"/>
       <c r="C186" s="12"/>
       <c r="D186" s="12"/>
       <c r="E186" s="12"/>
       <c r="F186" s="12"/>
-      <c r="G186" s="7"/>
-      <c r="H186" s="17"/>
-      <c r="I186" s="7"/>
+      <c r="G186" s="12"/>
+      <c r="H186" s="7"/>
+      <c r="I186" s="17"/>
       <c r="J186" s="7"/>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -5262,17 +5488,18 @@
       <c r="T186" s="7"/>
       <c r="U186" s="7"/>
       <c r="V186" s="7"/>
-    </row>
-    <row r="187" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W186" s="7"/>
+    </row>
+    <row r="187" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="9"/>
       <c r="B187" s="5"/>
       <c r="C187" s="12"/>
       <c r="D187" s="12"/>
       <c r="E187" s="12"/>
       <c r="F187" s="12"/>
-      <c r="G187" s="7"/>
-      <c r="H187" s="17"/>
-      <c r="I187" s="7"/>
+      <c r="G187" s="12"/>
+      <c r="H187" s="7"/>
+      <c r="I187" s="17"/>
       <c r="J187" s="7"/>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -5286,17 +5513,18 @@
       <c r="T187" s="7"/>
       <c r="U187" s="7"/>
       <c r="V187" s="7"/>
-    </row>
-    <row r="188" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W187" s="7"/>
+    </row>
+    <row r="188" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="9"/>
       <c r="B188" s="5"/>
       <c r="C188" s="12"/>
       <c r="D188" s="12"/>
       <c r="E188" s="12"/>
       <c r="F188" s="12"/>
-      <c r="G188" s="7"/>
-      <c r="H188" s="17"/>
-      <c r="I188" s="7"/>
+      <c r="G188" s="12"/>
+      <c r="H188" s="7"/>
+      <c r="I188" s="17"/>
       <c r="J188" s="7"/>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -5310,17 +5538,18 @@
       <c r="T188" s="7"/>
       <c r="U188" s="7"/>
       <c r="V188" s="7"/>
-    </row>
-    <row r="189" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W188" s="7"/>
+    </row>
+    <row r="189" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="9"/>
       <c r="B189" s="5"/>
       <c r="C189" s="12"/>
       <c r="D189" s="12"/>
       <c r="E189" s="12"/>
       <c r="F189" s="12"/>
-      <c r="G189" s="7"/>
-      <c r="H189" s="17"/>
-      <c r="I189" s="7"/>
+      <c r="G189" s="12"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="17"/>
       <c r="J189" s="7"/>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -5334,17 +5563,18 @@
       <c r="T189" s="7"/>
       <c r="U189" s="7"/>
       <c r="V189" s="7"/>
-    </row>
-    <row r="190" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W189" s="7"/>
+    </row>
+    <row r="190" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="9"/>
       <c r="B190" s="5"/>
       <c r="C190" s="12"/>
       <c r="D190" s="12"/>
       <c r="E190" s="12"/>
       <c r="F190" s="12"/>
-      <c r="G190" s="7"/>
-      <c r="H190" s="17"/>
-      <c r="I190" s="7"/>
+      <c r="G190" s="12"/>
+      <c r="H190" s="7"/>
+      <c r="I190" s="17"/>
       <c r="J190" s="7"/>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -5358,17 +5588,18 @@
       <c r="T190" s="7"/>
       <c r="U190" s="7"/>
       <c r="V190" s="7"/>
-    </row>
-    <row r="191" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W190" s="7"/>
+    </row>
+    <row r="191" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="9"/>
       <c r="B191" s="5"/>
       <c r="C191" s="12"/>
       <c r="D191" s="12"/>
       <c r="E191" s="12"/>
       <c r="F191" s="12"/>
-      <c r="G191" s="7"/>
-      <c r="H191" s="17"/>
-      <c r="I191" s="7"/>
+      <c r="G191" s="12"/>
+      <c r="H191" s="7"/>
+      <c r="I191" s="17"/>
       <c r="J191" s="7"/>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -5382,17 +5613,18 @@
       <c r="T191" s="7"/>
       <c r="U191" s="7"/>
       <c r="V191" s="7"/>
-    </row>
-    <row r="192" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W191" s="7"/>
+    </row>
+    <row r="192" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="9"/>
       <c r="B192" s="5"/>
       <c r="C192" s="12"/>
       <c r="D192" s="12"/>
       <c r="E192" s="12"/>
       <c r="F192" s="12"/>
-      <c r="G192" s="7"/>
-      <c r="H192" s="17"/>
-      <c r="I192" s="7"/>
+      <c r="G192" s="12"/>
+      <c r="H192" s="7"/>
+      <c r="I192" s="17"/>
       <c r="J192" s="7"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -5406,17 +5638,18 @@
       <c r="T192" s="7"/>
       <c r="U192" s="7"/>
       <c r="V192" s="7"/>
-    </row>
-    <row r="193" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W192" s="7"/>
+    </row>
+    <row r="193" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="9"/>
       <c r="B193" s="5"/>
       <c r="C193" s="12"/>
       <c r="D193" s="12"/>
       <c r="E193" s="12"/>
       <c r="F193" s="12"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="17"/>
-      <c r="I193" s="7"/>
+      <c r="G193" s="12"/>
+      <c r="H193" s="7"/>
+      <c r="I193" s="17"/>
       <c r="J193" s="7"/>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -5430,17 +5663,18 @@
       <c r="T193" s="7"/>
       <c r="U193" s="7"/>
       <c r="V193" s="7"/>
-    </row>
-    <row r="194" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W193" s="7"/>
+    </row>
+    <row r="194" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="9"/>
       <c r="B194" s="5"/>
       <c r="C194" s="12"/>
       <c r="D194" s="12"/>
       <c r="E194" s="12"/>
       <c r="F194" s="12"/>
-      <c r="G194" s="7"/>
-      <c r="H194" s="17"/>
-      <c r="I194" s="7"/>
+      <c r="G194" s="12"/>
+      <c r="H194" s="7"/>
+      <c r="I194" s="17"/>
       <c r="J194" s="7"/>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -5454,17 +5688,18 @@
       <c r="T194" s="7"/>
       <c r="U194" s="7"/>
       <c r="V194" s="7"/>
-    </row>
-    <row r="195" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W194" s="7"/>
+    </row>
+    <row r="195" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="9"/>
       <c r="B195" s="5"/>
       <c r="C195" s="12"/>
       <c r="D195" s="12"/>
       <c r="E195" s="12"/>
       <c r="F195" s="12"/>
-      <c r="G195" s="7"/>
-      <c r="H195" s="17"/>
-      <c r="I195" s="7"/>
+      <c r="G195" s="12"/>
+      <c r="H195" s="7"/>
+      <c r="I195" s="17"/>
       <c r="J195" s="7"/>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -5478,17 +5713,18 @@
       <c r="T195" s="7"/>
       <c r="U195" s="7"/>
       <c r="V195" s="7"/>
-    </row>
-    <row r="196" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W195" s="7"/>
+    </row>
+    <row r="196" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="9"/>
       <c r="B196" s="5"/>
       <c r="C196" s="12"/>
       <c r="D196" s="12"/>
       <c r="E196" s="12"/>
       <c r="F196" s="12"/>
-      <c r="G196" s="7"/>
-      <c r="H196" s="17"/>
-      <c r="I196" s="7"/>
+      <c r="G196" s="12"/>
+      <c r="H196" s="7"/>
+      <c r="I196" s="17"/>
       <c r="J196" s="7"/>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -5502,17 +5738,18 @@
       <c r="T196" s="7"/>
       <c r="U196" s="7"/>
       <c r="V196" s="7"/>
-    </row>
-    <row r="197" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W196" s="7"/>
+    </row>
+    <row r="197" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="9"/>
       <c r="B197" s="5"/>
       <c r="C197" s="12"/>
       <c r="D197" s="12"/>
       <c r="E197" s="12"/>
       <c r="F197" s="12"/>
-      <c r="G197" s="7"/>
-      <c r="H197" s="17"/>
-      <c r="I197" s="7"/>
+      <c r="G197" s="12"/>
+      <c r="H197" s="7"/>
+      <c r="I197" s="17"/>
       <c r="J197" s="7"/>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -5526,17 +5763,18 @@
       <c r="T197" s="7"/>
       <c r="U197" s="7"/>
       <c r="V197" s="7"/>
-    </row>
-    <row r="198" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W197" s="7"/>
+    </row>
+    <row r="198" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="9"/>
       <c r="B198" s="5"/>
       <c r="C198" s="12"/>
       <c r="D198" s="12"/>
       <c r="E198" s="12"/>
       <c r="F198" s="12"/>
-      <c r="G198" s="7"/>
-      <c r="H198" s="17"/>
-      <c r="I198" s="7"/>
+      <c r="G198" s="12"/>
+      <c r="H198" s="7"/>
+      <c r="I198" s="17"/>
       <c r="J198" s="7"/>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -5550,17 +5788,18 @@
       <c r="T198" s="7"/>
       <c r="U198" s="7"/>
       <c r="V198" s="7"/>
-    </row>
-    <row r="199" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W198" s="7"/>
+    </row>
+    <row r="199" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="9"/>
       <c r="B199" s="5"/>
       <c r="C199" s="12"/>
       <c r="D199" s="12"/>
       <c r="E199" s="12"/>
       <c r="F199" s="12"/>
-      <c r="G199" s="7"/>
-      <c r="H199" s="17"/>
-      <c r="I199" s="7"/>
+      <c r="G199" s="12"/>
+      <c r="H199" s="7"/>
+      <c r="I199" s="17"/>
       <c r="J199" s="7"/>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -5574,17 +5813,18 @@
       <c r="T199" s="7"/>
       <c r="U199" s="7"/>
       <c r="V199" s="7"/>
-    </row>
-    <row r="200" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W199" s="7"/>
+    </row>
+    <row r="200" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="9"/>
       <c r="B200" s="5"/>
       <c r="C200" s="12"/>
       <c r="D200" s="12"/>
       <c r="E200" s="12"/>
       <c r="F200" s="12"/>
-      <c r="G200" s="7"/>
-      <c r="H200" s="17"/>
-      <c r="I200" s="7"/>
+      <c r="G200" s="12"/>
+      <c r="H200" s="7"/>
+      <c r="I200" s="17"/>
       <c r="J200" s="7"/>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -5598,17 +5838,18 @@
       <c r="T200" s="7"/>
       <c r="U200" s="7"/>
       <c r="V200" s="7"/>
-    </row>
-    <row r="201" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W200" s="7"/>
+    </row>
+    <row r="201" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="9"/>
       <c r="B201" s="5"/>
       <c r="C201" s="12"/>
       <c r="D201" s="12"/>
       <c r="E201" s="12"/>
       <c r="F201" s="12"/>
-      <c r="G201" s="7"/>
-      <c r="H201" s="17"/>
-      <c r="I201" s="7"/>
+      <c r="G201" s="12"/>
+      <c r="H201" s="7"/>
+      <c r="I201" s="17"/>
       <c r="J201" s="7"/>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -5622,17 +5863,18 @@
       <c r="T201" s="7"/>
       <c r="U201" s="7"/>
       <c r="V201" s="7"/>
-    </row>
-    <row r="202" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W201" s="7"/>
+    </row>
+    <row r="202" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="9"/>
       <c r="B202" s="5"/>
       <c r="C202" s="12"/>
       <c r="D202" s="12"/>
       <c r="E202" s="12"/>
       <c r="F202" s="12"/>
-      <c r="G202" s="7"/>
-      <c r="H202" s="17"/>
-      <c r="I202" s="7"/>
+      <c r="G202" s="12"/>
+      <c r="H202" s="7"/>
+      <c r="I202" s="17"/>
       <c r="J202" s="7"/>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -5646,17 +5888,18 @@
       <c r="T202" s="7"/>
       <c r="U202" s="7"/>
       <c r="V202" s="7"/>
-    </row>
-    <row r="203" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W202" s="7"/>
+    </row>
+    <row r="203" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="9"/>
       <c r="B203" s="5"/>
       <c r="C203" s="12"/>
       <c r="D203" s="12"/>
       <c r="E203" s="12"/>
       <c r="F203" s="12"/>
-      <c r="G203" s="7"/>
-      <c r="H203" s="17"/>
-      <c r="I203" s="7"/>
+      <c r="G203" s="12"/>
+      <c r="H203" s="7"/>
+      <c r="I203" s="17"/>
       <c r="J203" s="7"/>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -5670,17 +5913,18 @@
       <c r="T203" s="7"/>
       <c r="U203" s="7"/>
       <c r="V203" s="7"/>
-    </row>
-    <row r="204" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W203" s="7"/>
+    </row>
+    <row r="204" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="9"/>
       <c r="B204" s="5"/>
       <c r="C204" s="12"/>
       <c r="D204" s="12"/>
       <c r="E204" s="12"/>
       <c r="F204" s="12"/>
-      <c r="G204" s="7"/>
-      <c r="H204" s="17"/>
-      <c r="I204" s="7"/>
+      <c r="G204" s="12"/>
+      <c r="H204" s="7"/>
+      <c r="I204" s="17"/>
       <c r="J204" s="7"/>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -5694,17 +5938,18 @@
       <c r="T204" s="7"/>
       <c r="U204" s="7"/>
       <c r="V204" s="7"/>
-    </row>
-    <row r="205" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W204" s="7"/>
+    </row>
+    <row r="205" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="9"/>
       <c r="B205" s="5"/>
       <c r="C205" s="12"/>
       <c r="D205" s="12"/>
       <c r="E205" s="12"/>
       <c r="F205" s="12"/>
-      <c r="G205" s="7"/>
-      <c r="H205" s="17"/>
-      <c r="I205" s="7"/>
+      <c r="G205" s="12"/>
+      <c r="H205" s="7"/>
+      <c r="I205" s="17"/>
       <c r="J205" s="7"/>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -5718,17 +5963,18 @@
       <c r="T205" s="7"/>
       <c r="U205" s="7"/>
       <c r="V205" s="7"/>
-    </row>
-    <row r="206" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W205" s="7"/>
+    </row>
+    <row r="206" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="9"/>
       <c r="B206" s="5"/>
       <c r="C206" s="12"/>
       <c r="D206" s="12"/>
       <c r="E206" s="12"/>
       <c r="F206" s="12"/>
-      <c r="G206" s="7"/>
-      <c r="H206" s="17"/>
-      <c r="I206" s="7"/>
+      <c r="G206" s="12"/>
+      <c r="H206" s="7"/>
+      <c r="I206" s="17"/>
       <c r="J206" s="7"/>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -5742,17 +5988,18 @@
       <c r="T206" s="7"/>
       <c r="U206" s="7"/>
       <c r="V206" s="7"/>
-    </row>
-    <row r="207" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W206" s="7"/>
+    </row>
+    <row r="207" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="9"/>
       <c r="B207" s="5"/>
       <c r="C207" s="12"/>
       <c r="D207" s="12"/>
       <c r="E207" s="12"/>
       <c r="F207" s="12"/>
-      <c r="G207" s="7"/>
-      <c r="H207" s="17"/>
-      <c r="I207" s="7"/>
+      <c r="G207" s="12"/>
+      <c r="H207" s="7"/>
+      <c r="I207" s="17"/>
       <c r="J207" s="7"/>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -5766,17 +6013,18 @@
       <c r="T207" s="7"/>
       <c r="U207" s="7"/>
       <c r="V207" s="7"/>
-    </row>
-    <row r="208" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W207" s="7"/>
+    </row>
+    <row r="208" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="9"/>
       <c r="B208" s="5"/>
       <c r="C208" s="12"/>
       <c r="D208" s="12"/>
       <c r="E208" s="12"/>
       <c r="F208" s="12"/>
-      <c r="G208" s="7"/>
-      <c r="H208" s="17"/>
-      <c r="I208" s="7"/>
+      <c r="G208" s="12"/>
+      <c r="H208" s="7"/>
+      <c r="I208" s="17"/>
       <c r="J208" s="7"/>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -5790,17 +6038,18 @@
       <c r="T208" s="7"/>
       <c r="U208" s="7"/>
       <c r="V208" s="7"/>
-    </row>
-    <row r="209" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W208" s="7"/>
+    </row>
+    <row r="209" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="9"/>
       <c r="B209" s="5"/>
       <c r="C209" s="12"/>
       <c r="D209" s="12"/>
       <c r="E209" s="12"/>
       <c r="F209" s="12"/>
-      <c r="G209" s="7"/>
-      <c r="H209" s="17"/>
-      <c r="I209" s="7"/>
+      <c r="G209" s="12"/>
+      <c r="H209" s="7"/>
+      <c r="I209" s="17"/>
       <c r="J209" s="7"/>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -5814,17 +6063,18 @@
       <c r="T209" s="7"/>
       <c r="U209" s="7"/>
       <c r="V209" s="7"/>
-    </row>
-    <row r="210" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W209" s="7"/>
+    </row>
+    <row r="210" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="9"/>
       <c r="B210" s="5"/>
       <c r="C210" s="12"/>
       <c r="D210" s="12"/>
       <c r="E210" s="12"/>
       <c r="F210" s="12"/>
-      <c r="G210" s="7"/>
-      <c r="H210" s="17"/>
-      <c r="I210" s="7"/>
+      <c r="G210" s="12"/>
+      <c r="H210" s="7"/>
+      <c r="I210" s="17"/>
       <c r="J210" s="7"/>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -5838,17 +6088,18 @@
       <c r="T210" s="7"/>
       <c r="U210" s="7"/>
       <c r="V210" s="7"/>
-    </row>
-    <row r="211" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W210" s="7"/>
+    </row>
+    <row r="211" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="9"/>
       <c r="B211" s="5"/>
       <c r="C211" s="12"/>
       <c r="D211" s="12"/>
       <c r="E211" s="12"/>
       <c r="F211" s="12"/>
-      <c r="G211" s="7"/>
-      <c r="H211" s="17"/>
-      <c r="I211" s="7"/>
+      <c r="G211" s="12"/>
+      <c r="H211" s="7"/>
+      <c r="I211" s="17"/>
       <c r="J211" s="7"/>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -5862,17 +6113,18 @@
       <c r="T211" s="7"/>
       <c r="U211" s="7"/>
       <c r="V211" s="7"/>
-    </row>
-    <row r="212" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W211" s="7"/>
+    </row>
+    <row r="212" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="9"/>
       <c r="B212" s="5"/>
       <c r="C212" s="12"/>
       <c r="D212" s="12"/>
       <c r="E212" s="12"/>
       <c r="F212" s="12"/>
-      <c r="G212" s="7"/>
-      <c r="H212" s="17"/>
-      <c r="I212" s="7"/>
+      <c r="G212" s="12"/>
+      <c r="H212" s="7"/>
+      <c r="I212" s="17"/>
       <c r="J212" s="7"/>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -5886,17 +6138,18 @@
       <c r="T212" s="7"/>
       <c r="U212" s="7"/>
       <c r="V212" s="7"/>
-    </row>
-    <row r="213" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W212" s="7"/>
+    </row>
+    <row r="213" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="9"/>
       <c r="B213" s="5"/>
       <c r="C213" s="12"/>
       <c r="D213" s="12"/>
       <c r="E213" s="12"/>
       <c r="F213" s="12"/>
-      <c r="G213" s="7"/>
-      <c r="H213" s="17"/>
-      <c r="I213" s="7"/>
+      <c r="G213" s="12"/>
+      <c r="H213" s="7"/>
+      <c r="I213" s="17"/>
       <c r="J213" s="7"/>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -5910,17 +6163,18 @@
       <c r="T213" s="7"/>
       <c r="U213" s="7"/>
       <c r="V213" s="7"/>
-    </row>
-    <row r="214" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W213" s="7"/>
+    </row>
+    <row r="214" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="9"/>
       <c r="B214" s="5"/>
       <c r="C214" s="12"/>
       <c r="D214" s="12"/>
       <c r="E214" s="12"/>
       <c r="F214" s="12"/>
-      <c r="G214" s="7"/>
-      <c r="H214" s="17"/>
-      <c r="I214" s="7"/>
+      <c r="G214" s="12"/>
+      <c r="H214" s="7"/>
+      <c r="I214" s="17"/>
       <c r="J214" s="7"/>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -5934,17 +6188,18 @@
       <c r="T214" s="7"/>
       <c r="U214" s="7"/>
       <c r="V214" s="7"/>
-    </row>
-    <row r="215" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W214" s="7"/>
+    </row>
+    <row r="215" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="9"/>
       <c r="B215" s="5"/>
       <c r="C215" s="12"/>
       <c r="D215" s="12"/>
       <c r="E215" s="12"/>
       <c r="F215" s="12"/>
-      <c r="G215" s="7"/>
-      <c r="H215" s="17"/>
-      <c r="I215" s="7"/>
+      <c r="G215" s="12"/>
+      <c r="H215" s="7"/>
+      <c r="I215" s="17"/>
       <c r="J215" s="7"/>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -5958,17 +6213,18 @@
       <c r="T215" s="7"/>
       <c r="U215" s="7"/>
       <c r="V215" s="7"/>
-    </row>
-    <row r="216" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W215" s="7"/>
+    </row>
+    <row r="216" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="9"/>
       <c r="B216" s="5"/>
       <c r="C216" s="12"/>
       <c r="D216" s="12"/>
       <c r="E216" s="12"/>
       <c r="F216" s="12"/>
-      <c r="G216" s="7"/>
-      <c r="H216" s="17"/>
-      <c r="I216" s="7"/>
+      <c r="G216" s="12"/>
+      <c r="H216" s="7"/>
+      <c r="I216" s="17"/>
       <c r="J216" s="7"/>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -5982,17 +6238,18 @@
       <c r="T216" s="7"/>
       <c r="U216" s="7"/>
       <c r="V216" s="7"/>
-    </row>
-    <row r="217" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W216" s="7"/>
+    </row>
+    <row r="217" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="9"/>
       <c r="B217" s="5"/>
       <c r="C217" s="12"/>
       <c r="D217" s="12"/>
       <c r="E217" s="12"/>
       <c r="F217" s="12"/>
-      <c r="G217" s="7"/>
-      <c r="H217" s="17"/>
-      <c r="I217" s="7"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="7"/>
+      <c r="I217" s="17"/>
       <c r="J217" s="7"/>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -6006,17 +6263,18 @@
       <c r="T217" s="7"/>
       <c r="U217" s="7"/>
       <c r="V217" s="7"/>
-    </row>
-    <row r="218" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W217" s="7"/>
+    </row>
+    <row r="218" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="9"/>
       <c r="B218" s="5"/>
       <c r="C218" s="12"/>
       <c r="D218" s="12"/>
       <c r="E218" s="12"/>
       <c r="F218" s="12"/>
-      <c r="G218" s="7"/>
-      <c r="H218" s="17"/>
-      <c r="I218" s="7"/>
+      <c r="G218" s="12"/>
+      <c r="H218" s="7"/>
+      <c r="I218" s="17"/>
       <c r="J218" s="7"/>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -6030,17 +6288,18 @@
       <c r="T218" s="7"/>
       <c r="U218" s="7"/>
       <c r="V218" s="7"/>
-    </row>
-    <row r="219" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W218" s="7"/>
+    </row>
+    <row r="219" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="9"/>
       <c r="B219" s="5"/>
       <c r="C219" s="12"/>
       <c r="D219" s="12"/>
       <c r="E219" s="12"/>
       <c r="F219" s="12"/>
-      <c r="G219" s="7"/>
-      <c r="H219" s="17"/>
-      <c r="I219" s="7"/>
+      <c r="G219" s="12"/>
+      <c r="H219" s="7"/>
+      <c r="I219" s="17"/>
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -6054,17 +6313,18 @@
       <c r="T219" s="7"/>
       <c r="U219" s="7"/>
       <c r="V219" s="7"/>
-    </row>
-    <row r="220" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W219" s="7"/>
+    </row>
+    <row r="220" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="9"/>
       <c r="B220" s="5"/>
       <c r="C220" s="12"/>
       <c r="D220" s="12"/>
       <c r="E220" s="12"/>
       <c r="F220" s="12"/>
-      <c r="G220" s="7"/>
-      <c r="H220" s="17"/>
-      <c r="I220" s="7"/>
+      <c r="G220" s="12"/>
+      <c r="H220" s="7"/>
+      <c r="I220" s="17"/>
       <c r="J220" s="7"/>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -6078,17 +6338,18 @@
       <c r="T220" s="7"/>
       <c r="U220" s="7"/>
       <c r="V220" s="7"/>
-    </row>
-    <row r="221" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W220" s="7"/>
+    </row>
+    <row r="221" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="9"/>
       <c r="B221" s="5"/>
       <c r="C221" s="12"/>
       <c r="D221" s="12"/>
       <c r="E221" s="12"/>
       <c r="F221" s="12"/>
-      <c r="G221" s="7"/>
-      <c r="H221" s="17"/>
-      <c r="I221" s="7"/>
+      <c r="G221" s="12"/>
+      <c r="H221" s="7"/>
+      <c r="I221" s="17"/>
       <c r="J221" s="7"/>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -6102,17 +6363,18 @@
       <c r="T221" s="7"/>
       <c r="U221" s="7"/>
       <c r="V221" s="7"/>
-    </row>
-    <row r="222" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W221" s="7"/>
+    </row>
+    <row r="222" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="9"/>
       <c r="B222" s="5"/>
       <c r="C222" s="12"/>
       <c r="D222" s="12"/>
       <c r="E222" s="12"/>
       <c r="F222" s="12"/>
-      <c r="G222" s="7"/>
-      <c r="H222" s="17"/>
-      <c r="I222" s="7"/>
+      <c r="G222" s="12"/>
+      <c r="H222" s="7"/>
+      <c r="I222" s="17"/>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -6126,17 +6388,18 @@
       <c r="T222" s="7"/>
       <c r="U222" s="7"/>
       <c r="V222" s="7"/>
-    </row>
-    <row r="223" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W222" s="7"/>
+    </row>
+    <row r="223" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="9"/>
       <c r="B223" s="5"/>
       <c r="C223" s="12"/>
       <c r="D223" s="12"/>
       <c r="E223" s="12"/>
       <c r="F223" s="12"/>
-      <c r="G223" s="7"/>
-      <c r="H223" s="17"/>
-      <c r="I223" s="7"/>
+      <c r="G223" s="12"/>
+      <c r="H223" s="7"/>
+      <c r="I223" s="17"/>
       <c r="J223" s="7"/>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -6150,17 +6413,18 @@
       <c r="T223" s="7"/>
       <c r="U223" s="7"/>
       <c r="V223" s="7"/>
-    </row>
-    <row r="224" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W223" s="7"/>
+    </row>
+    <row r="224" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="9"/>
       <c r="B224" s="5"/>
       <c r="C224" s="12"/>
       <c r="D224" s="12"/>
       <c r="E224" s="12"/>
       <c r="F224" s="12"/>
-      <c r="G224" s="7"/>
-      <c r="H224" s="17"/>
-      <c r="I224" s="7"/>
+      <c r="G224" s="12"/>
+      <c r="H224" s="7"/>
+      <c r="I224" s="17"/>
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -6174,17 +6438,18 @@
       <c r="T224" s="7"/>
       <c r="U224" s="7"/>
       <c r="V224" s="7"/>
-    </row>
-    <row r="225" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W224" s="7"/>
+    </row>
+    <row r="225" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="9"/>
       <c r="B225" s="5"/>
       <c r="C225" s="12"/>
       <c r="D225" s="12"/>
       <c r="E225" s="12"/>
       <c r="F225" s="12"/>
-      <c r="G225" s="7"/>
-      <c r="H225" s="17"/>
-      <c r="I225" s="7"/>
+      <c r="G225" s="12"/>
+      <c r="H225" s="7"/>
+      <c r="I225" s="17"/>
       <c r="J225" s="7"/>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -6198,17 +6463,18 @@
       <c r="T225" s="7"/>
       <c r="U225" s="7"/>
       <c r="V225" s="7"/>
-    </row>
-    <row r="226" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W225" s="7"/>
+    </row>
+    <row r="226" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="9"/>
       <c r="B226" s="5"/>
       <c r="C226" s="12"/>
       <c r="D226" s="12"/>
       <c r="E226" s="12"/>
       <c r="F226" s="12"/>
-      <c r="G226" s="7"/>
-      <c r="H226" s="17"/>
-      <c r="I226" s="7"/>
+      <c r="G226" s="12"/>
+      <c r="H226" s="7"/>
+      <c r="I226" s="17"/>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -6222,17 +6488,18 @@
       <c r="T226" s="7"/>
       <c r="U226" s="7"/>
       <c r="V226" s="7"/>
-    </row>
-    <row r="227" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W226" s="7"/>
+    </row>
+    <row r="227" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="9"/>
       <c r="B227" s="5"/>
       <c r="C227" s="12"/>
       <c r="D227" s="12"/>
       <c r="E227" s="12"/>
       <c r="F227" s="12"/>
-      <c r="G227" s="7"/>
-      <c r="H227" s="17"/>
-      <c r="I227" s="7"/>
+      <c r="G227" s="12"/>
+      <c r="H227" s="7"/>
+      <c r="I227" s="17"/>
       <c r="J227" s="7"/>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -6246,17 +6513,18 @@
       <c r="T227" s="7"/>
       <c r="U227" s="7"/>
       <c r="V227" s="7"/>
-    </row>
-    <row r="228" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W227" s="7"/>
+    </row>
+    <row r="228" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="9"/>
       <c r="B228" s="5"/>
       <c r="C228" s="12"/>
       <c r="D228" s="12"/>
       <c r="E228" s="12"/>
       <c r="F228" s="12"/>
-      <c r="G228" s="7"/>
-      <c r="H228" s="17"/>
-      <c r="I228" s="7"/>
+      <c r="G228" s="12"/>
+      <c r="H228" s="7"/>
+      <c r="I228" s="17"/>
       <c r="J228" s="7"/>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -6270,17 +6538,18 @@
       <c r="T228" s="7"/>
       <c r="U228" s="7"/>
       <c r="V228" s="7"/>
-    </row>
-    <row r="229" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W228" s="7"/>
+    </row>
+    <row r="229" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="9"/>
       <c r="B229" s="5"/>
       <c r="C229" s="12"/>
       <c r="D229" s="12"/>
       <c r="E229" s="12"/>
       <c r="F229" s="12"/>
-      <c r="G229" s="7"/>
-      <c r="H229" s="17"/>
-      <c r="I229" s="7"/>
+      <c r="G229" s="12"/>
+      <c r="H229" s="7"/>
+      <c r="I229" s="17"/>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -6294,17 +6563,18 @@
       <c r="T229" s="7"/>
       <c r="U229" s="7"/>
       <c r="V229" s="7"/>
-    </row>
-    <row r="230" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W229" s="7"/>
+    </row>
+    <row r="230" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="9"/>
       <c r="B230" s="5"/>
       <c r="C230" s="12"/>
       <c r="D230" s="12"/>
       <c r="E230" s="12"/>
       <c r="F230" s="12"/>
-      <c r="G230" s="7"/>
-      <c r="H230" s="17"/>
-      <c r="I230" s="7"/>
+      <c r="G230" s="12"/>
+      <c r="H230" s="7"/>
+      <c r="I230" s="17"/>
       <c r="J230" s="7"/>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -6318,17 +6588,18 @@
       <c r="T230" s="7"/>
       <c r="U230" s="7"/>
       <c r="V230" s="7"/>
-    </row>
-    <row r="231" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W230" s="7"/>
+    </row>
+    <row r="231" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="9"/>
       <c r="B231" s="5"/>
       <c r="C231" s="12"/>
       <c r="D231" s="12"/>
       <c r="E231" s="12"/>
       <c r="F231" s="12"/>
-      <c r="G231" s="7"/>
-      <c r="H231" s="17"/>
-      <c r="I231" s="7"/>
+      <c r="G231" s="12"/>
+      <c r="H231" s="7"/>
+      <c r="I231" s="17"/>
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -6342,17 +6613,18 @@
       <c r="T231" s="7"/>
       <c r="U231" s="7"/>
       <c r="V231" s="7"/>
-    </row>
-    <row r="232" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W231" s="7"/>
+    </row>
+    <row r="232" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="9"/>
       <c r="B232" s="5"/>
       <c r="C232" s="12"/>
       <c r="D232" s="12"/>
       <c r="E232" s="12"/>
       <c r="F232" s="12"/>
-      <c r="G232" s="7"/>
-      <c r="H232" s="17"/>
-      <c r="I232" s="7"/>
+      <c r="G232" s="12"/>
+      <c r="H232" s="7"/>
+      <c r="I232" s="17"/>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -6366,17 +6638,18 @@
       <c r="T232" s="7"/>
       <c r="U232" s="7"/>
       <c r="V232" s="7"/>
-    </row>
-    <row r="233" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W232" s="7"/>
+    </row>
+    <row r="233" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="9"/>
       <c r="B233" s="5"/>
       <c r="C233" s="12"/>
       <c r="D233" s="12"/>
       <c r="E233" s="12"/>
       <c r="F233" s="12"/>
-      <c r="G233" s="7"/>
-      <c r="H233" s="17"/>
-      <c r="I233" s="7"/>
+      <c r="G233" s="12"/>
+      <c r="H233" s="7"/>
+      <c r="I233" s="17"/>
       <c r="J233" s="7"/>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -6390,17 +6663,18 @@
       <c r="T233" s="7"/>
       <c r="U233" s="7"/>
       <c r="V233" s="7"/>
-    </row>
-    <row r="234" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W233" s="7"/>
+    </row>
+    <row r="234" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="9"/>
       <c r="B234" s="5"/>
       <c r="C234" s="12"/>
       <c r="D234" s="12"/>
       <c r="E234" s="12"/>
       <c r="F234" s="12"/>
-      <c r="G234" s="7"/>
-      <c r="H234" s="17"/>
-      <c r="I234" s="7"/>
+      <c r="G234" s="12"/>
+      <c r="H234" s="7"/>
+      <c r="I234" s="17"/>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -6414,17 +6688,18 @@
       <c r="T234" s="7"/>
       <c r="U234" s="7"/>
       <c r="V234" s="7"/>
-    </row>
-    <row r="235" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W234" s="7"/>
+    </row>
+    <row r="235" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="9"/>
       <c r="B235" s="5"/>
       <c r="C235" s="12"/>
       <c r="D235" s="12"/>
       <c r="E235" s="12"/>
       <c r="F235" s="12"/>
-      <c r="G235" s="7"/>
-      <c r="H235" s="17"/>
-      <c r="I235" s="7"/>
+      <c r="G235" s="12"/>
+      <c r="H235" s="7"/>
+      <c r="I235" s="17"/>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -6438,17 +6713,18 @@
       <c r="T235" s="7"/>
       <c r="U235" s="7"/>
       <c r="V235" s="7"/>
-    </row>
-    <row r="236" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W235" s="7"/>
+    </row>
+    <row r="236" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="9"/>
       <c r="B236" s="5"/>
       <c r="C236" s="12"/>
       <c r="D236" s="12"/>
       <c r="E236" s="12"/>
       <c r="F236" s="12"/>
-      <c r="G236" s="7"/>
-      <c r="H236" s="17"/>
-      <c r="I236" s="7"/>
+      <c r="G236" s="12"/>
+      <c r="H236" s="7"/>
+      <c r="I236" s="17"/>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -6462,17 +6738,18 @@
       <c r="T236" s="7"/>
       <c r="U236" s="7"/>
       <c r="V236" s="7"/>
-    </row>
-    <row r="237" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W236" s="7"/>
+    </row>
+    <row r="237" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="9"/>
       <c r="B237" s="5"/>
       <c r="C237" s="12"/>
       <c r="D237" s="12"/>
       <c r="E237" s="12"/>
       <c r="F237" s="12"/>
-      <c r="G237" s="7"/>
-      <c r="H237" s="17"/>
-      <c r="I237" s="7"/>
+      <c r="G237" s="12"/>
+      <c r="H237" s="7"/>
+      <c r="I237" s="17"/>
       <c r="J237" s="7"/>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -6486,17 +6763,18 @@
       <c r="T237" s="7"/>
       <c r="U237" s="7"/>
       <c r="V237" s="7"/>
-    </row>
-    <row r="238" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W237" s="7"/>
+    </row>
+    <row r="238" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="9"/>
       <c r="B238" s="5"/>
       <c r="C238" s="12"/>
       <c r="D238" s="12"/>
       <c r="E238" s="12"/>
       <c r="F238" s="12"/>
-      <c r="G238" s="7"/>
-      <c r="H238" s="17"/>
-      <c r="I238" s="7"/>
+      <c r="G238" s="12"/>
+      <c r="H238" s="7"/>
+      <c r="I238" s="17"/>
       <c r="J238" s="7"/>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -6510,17 +6788,18 @@
       <c r="T238" s="7"/>
       <c r="U238" s="7"/>
       <c r="V238" s="7"/>
-    </row>
-    <row r="239" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W238" s="7"/>
+    </row>
+    <row r="239" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="9"/>
       <c r="B239" s="5"/>
       <c r="C239" s="12"/>
       <c r="D239" s="12"/>
       <c r="E239" s="12"/>
       <c r="F239" s="12"/>
-      <c r="G239" s="7"/>
-      <c r="H239" s="17"/>
-      <c r="I239" s="7"/>
+      <c r="G239" s="12"/>
+      <c r="H239" s="7"/>
+      <c r="I239" s="17"/>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -6534,17 +6813,18 @@
       <c r="T239" s="7"/>
       <c r="U239" s="7"/>
       <c r="V239" s="7"/>
-    </row>
-    <row r="240" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W239" s="7"/>
+    </row>
+    <row r="240" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="9"/>
       <c r="B240" s="5"/>
       <c r="C240" s="12"/>
       <c r="D240" s="12"/>
       <c r="E240" s="12"/>
       <c r="F240" s="12"/>
-      <c r="G240" s="7"/>
-      <c r="H240" s="17"/>
-      <c r="I240" s="7"/>
+      <c r="G240" s="12"/>
+      <c r="H240" s="7"/>
+      <c r="I240" s="17"/>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -6558,17 +6838,18 @@
       <c r="T240" s="7"/>
       <c r="U240" s="7"/>
       <c r="V240" s="7"/>
-    </row>
-    <row r="241" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W240" s="7"/>
+    </row>
+    <row r="241" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="9"/>
       <c r="B241" s="5"/>
       <c r="C241" s="12"/>
       <c r="D241" s="12"/>
       <c r="E241" s="12"/>
       <c r="F241" s="12"/>
-      <c r="G241" s="7"/>
-      <c r="H241" s="17"/>
-      <c r="I241" s="7"/>
+      <c r="G241" s="12"/>
+      <c r="H241" s="7"/>
+      <c r="I241" s="17"/>
       <c r="J241" s="7"/>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -6582,17 +6863,18 @@
       <c r="T241" s="7"/>
       <c r="U241" s="7"/>
       <c r="V241" s="7"/>
-    </row>
-    <row r="242" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W241" s="7"/>
+    </row>
+    <row r="242" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="9"/>
       <c r="B242" s="5"/>
       <c r="C242" s="12"/>
       <c r="D242" s="12"/>
       <c r="E242" s="12"/>
       <c r="F242" s="12"/>
-      <c r="G242" s="7"/>
-      <c r="H242" s="17"/>
-      <c r="I242" s="7"/>
+      <c r="G242" s="12"/>
+      <c r="H242" s="7"/>
+      <c r="I242" s="17"/>
       <c r="J242" s="7"/>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -6606,17 +6888,18 @@
       <c r="T242" s="7"/>
       <c r="U242" s="7"/>
       <c r="V242" s="7"/>
-    </row>
-    <row r="243" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W242" s="7"/>
+    </row>
+    <row r="243" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="9"/>
       <c r="B243" s="5"/>
       <c r="C243" s="12"/>
       <c r="D243" s="12"/>
       <c r="E243" s="12"/>
       <c r="F243" s="12"/>
-      <c r="G243" s="7"/>
-      <c r="H243" s="17"/>
-      <c r="I243" s="7"/>
+      <c r="G243" s="12"/>
+      <c r="H243" s="7"/>
+      <c r="I243" s="17"/>
       <c r="J243" s="7"/>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -6630,17 +6913,18 @@
       <c r="T243" s="7"/>
       <c r="U243" s="7"/>
       <c r="V243" s="7"/>
-    </row>
-    <row r="244" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W243" s="7"/>
+    </row>
+    <row r="244" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="9"/>
       <c r="B244" s="5"/>
       <c r="C244" s="12"/>
       <c r="D244" s="12"/>
       <c r="E244" s="12"/>
       <c r="F244" s="12"/>
-      <c r="G244" s="7"/>
-      <c r="H244" s="17"/>
-      <c r="I244" s="7"/>
+      <c r="G244" s="12"/>
+      <c r="H244" s="7"/>
+      <c r="I244" s="17"/>
       <c r="J244" s="7"/>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -6654,17 +6938,18 @@
       <c r="T244" s="7"/>
       <c r="U244" s="7"/>
       <c r="V244" s="7"/>
-    </row>
-    <row r="245" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W244" s="7"/>
+    </row>
+    <row r="245" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="9"/>
       <c r="B245" s="5"/>
       <c r="C245" s="12"/>
       <c r="D245" s="12"/>
       <c r="E245" s="12"/>
       <c r="F245" s="12"/>
-      <c r="G245" s="7"/>
-      <c r="H245" s="17"/>
-      <c r="I245" s="7"/>
+      <c r="G245" s="12"/>
+      <c r="H245" s="7"/>
+      <c r="I245" s="17"/>
       <c r="J245" s="7"/>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -6678,17 +6963,18 @@
       <c r="T245" s="7"/>
       <c r="U245" s="7"/>
       <c r="V245" s="7"/>
-    </row>
-    <row r="246" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W245" s="7"/>
+    </row>
+    <row r="246" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="9"/>
       <c r="B246" s="5"/>
       <c r="C246" s="12"/>
       <c r="D246" s="12"/>
       <c r="E246" s="12"/>
       <c r="F246" s="12"/>
-      <c r="G246" s="7"/>
-      <c r="H246" s="17"/>
-      <c r="I246" s="7"/>
+      <c r="G246" s="12"/>
+      <c r="H246" s="7"/>
+      <c r="I246" s="17"/>
       <c r="J246" s="7"/>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -6702,17 +6988,18 @@
       <c r="T246" s="7"/>
       <c r="U246" s="7"/>
       <c r="V246" s="7"/>
-    </row>
-    <row r="247" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W246" s="7"/>
+    </row>
+    <row r="247" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="9"/>
       <c r="B247" s="5"/>
       <c r="C247" s="12"/>
       <c r="D247" s="12"/>
       <c r="E247" s="12"/>
       <c r="F247" s="12"/>
-      <c r="G247" s="7"/>
-      <c r="H247" s="17"/>
-      <c r="I247" s="7"/>
+      <c r="G247" s="12"/>
+      <c r="H247" s="7"/>
+      <c r="I247" s="17"/>
       <c r="J247" s="7"/>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -6726,17 +7013,18 @@
       <c r="T247" s="7"/>
       <c r="U247" s="7"/>
       <c r="V247" s="7"/>
-    </row>
-    <row r="248" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W247" s="7"/>
+    </row>
+    <row r="248" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="9"/>
       <c r="B248" s="5"/>
       <c r="C248" s="12"/>
       <c r="D248" s="12"/>
       <c r="E248" s="12"/>
       <c r="F248" s="12"/>
-      <c r="G248" s="7"/>
-      <c r="H248" s="17"/>
-      <c r="I248" s="7"/>
+      <c r="G248" s="12"/>
+      <c r="H248" s="7"/>
+      <c r="I248" s="17"/>
       <c r="J248" s="7"/>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -6750,17 +7038,18 @@
       <c r="T248" s="7"/>
       <c r="U248" s="7"/>
       <c r="V248" s="7"/>
-    </row>
-    <row r="249" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W248" s="7"/>
+    </row>
+    <row r="249" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="9"/>
       <c r="B249" s="5"/>
       <c r="C249" s="12"/>
       <c r="D249" s="12"/>
       <c r="E249" s="12"/>
       <c r="F249" s="12"/>
-      <c r="G249" s="7"/>
-      <c r="H249" s="17"/>
-      <c r="I249" s="7"/>
+      <c r="G249" s="12"/>
+      <c r="H249" s="7"/>
+      <c r="I249" s="17"/>
       <c r="J249" s="7"/>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -6774,17 +7063,18 @@
       <c r="T249" s="7"/>
       <c r="U249" s="7"/>
       <c r="V249" s="7"/>
-    </row>
-    <row r="250" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W249" s="7"/>
+    </row>
+    <row r="250" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="9"/>
       <c r="B250" s="5"/>
       <c r="C250" s="12"/>
       <c r="D250" s="12"/>
       <c r="E250" s="12"/>
       <c r="F250" s="12"/>
-      <c r="G250" s="7"/>
-      <c r="H250" s="17"/>
-      <c r="I250" s="7"/>
+      <c r="G250" s="12"/>
+      <c r="H250" s="7"/>
+      <c r="I250" s="17"/>
       <c r="J250" s="7"/>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -6798,17 +7088,18 @@
       <c r="T250" s="7"/>
       <c r="U250" s="7"/>
       <c r="V250" s="7"/>
-    </row>
-    <row r="251" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W250" s="7"/>
+    </row>
+    <row r="251" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="9"/>
       <c r="B251" s="5"/>
       <c r="C251" s="12"/>
       <c r="D251" s="12"/>
       <c r="E251" s="12"/>
       <c r="F251" s="12"/>
-      <c r="G251" s="7"/>
-      <c r="H251" s="17"/>
-      <c r="I251" s="7"/>
+      <c r="G251" s="12"/>
+      <c r="H251" s="7"/>
+      <c r="I251" s="17"/>
       <c r="J251" s="7"/>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -6822,17 +7113,18 @@
       <c r="T251" s="7"/>
       <c r="U251" s="7"/>
       <c r="V251" s="7"/>
-    </row>
-    <row r="252" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W251" s="7"/>
+    </row>
+    <row r="252" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="9"/>
       <c r="B252" s="5"/>
       <c r="C252" s="12"/>
       <c r="D252" s="12"/>
       <c r="E252" s="12"/>
       <c r="F252" s="12"/>
-      <c r="G252" s="7"/>
-      <c r="H252" s="17"/>
-      <c r="I252" s="7"/>
+      <c r="G252" s="12"/>
+      <c r="H252" s="7"/>
+      <c r="I252" s="17"/>
       <c r="J252" s="7"/>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -6846,17 +7138,18 @@
       <c r="T252" s="7"/>
       <c r="U252" s="7"/>
       <c r="V252" s="7"/>
-    </row>
-    <row r="253" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W252" s="7"/>
+    </row>
+    <row r="253" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="9"/>
       <c r="B253" s="5"/>
       <c r="C253" s="12"/>
       <c r="D253" s="12"/>
       <c r="E253" s="12"/>
       <c r="F253" s="12"/>
-      <c r="G253" s="7"/>
-      <c r="H253" s="17"/>
-      <c r="I253" s="7"/>
+      <c r="G253" s="12"/>
+      <c r="H253" s="7"/>
+      <c r="I253" s="17"/>
       <c r="J253" s="7"/>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -6870,17 +7163,18 @@
       <c r="T253" s="7"/>
       <c r="U253" s="7"/>
       <c r="V253" s="7"/>
-    </row>
-    <row r="254" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W253" s="7"/>
+    </row>
+    <row r="254" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="9"/>
       <c r="B254" s="5"/>
       <c r="C254" s="12"/>
       <c r="D254" s="12"/>
       <c r="E254" s="12"/>
       <c r="F254" s="12"/>
-      <c r="G254" s="7"/>
-      <c r="H254" s="17"/>
-      <c r="I254" s="7"/>
+      <c r="G254" s="12"/>
+      <c r="H254" s="7"/>
+      <c r="I254" s="17"/>
       <c r="J254" s="7"/>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -6894,17 +7188,18 @@
       <c r="T254" s="7"/>
       <c r="U254" s="7"/>
       <c r="V254" s="7"/>
-    </row>
-    <row r="255" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W254" s="7"/>
+    </row>
+    <row r="255" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="9"/>
       <c r="B255" s="5"/>
       <c r="C255" s="12"/>
       <c r="D255" s="12"/>
       <c r="E255" s="12"/>
       <c r="F255" s="12"/>
-      <c r="G255" s="7"/>
-      <c r="H255" s="17"/>
-      <c r="I255" s="7"/>
+      <c r="G255" s="12"/>
+      <c r="H255" s="7"/>
+      <c r="I255" s="17"/>
       <c r="J255" s="7"/>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -6918,17 +7213,18 @@
       <c r="T255" s="7"/>
       <c r="U255" s="7"/>
       <c r="V255" s="7"/>
-    </row>
-    <row r="256" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W255" s="7"/>
+    </row>
+    <row r="256" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="9"/>
       <c r="B256" s="5"/>
       <c r="C256" s="12"/>
       <c r="D256" s="12"/>
       <c r="E256" s="12"/>
       <c r="F256" s="12"/>
-      <c r="G256" s="7"/>
-      <c r="H256" s="17"/>
-      <c r="I256" s="7"/>
+      <c r="G256" s="12"/>
+      <c r="H256" s="7"/>
+      <c r="I256" s="17"/>
       <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -6942,17 +7238,18 @@
       <c r="T256" s="7"/>
       <c r="U256" s="7"/>
       <c r="V256" s="7"/>
-    </row>
-    <row r="257" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W256" s="7"/>
+    </row>
+    <row r="257" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="9"/>
       <c r="B257" s="5"/>
       <c r="C257" s="12"/>
       <c r="D257" s="12"/>
       <c r="E257" s="12"/>
       <c r="F257" s="12"/>
-      <c r="G257" s="7"/>
-      <c r="H257" s="17"/>
-      <c r="I257" s="7"/>
+      <c r="G257" s="12"/>
+      <c r="H257" s="7"/>
+      <c r="I257" s="17"/>
       <c r="J257" s="7"/>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -6966,17 +7263,18 @@
       <c r="T257" s="7"/>
       <c r="U257" s="7"/>
       <c r="V257" s="7"/>
-    </row>
-    <row r="258" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W257" s="7"/>
+    </row>
+    <row r="258" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="9"/>
       <c r="B258" s="5"/>
       <c r="C258" s="12"/>
       <c r="D258" s="12"/>
       <c r="E258" s="12"/>
       <c r="F258" s="12"/>
-      <c r="G258" s="7"/>
-      <c r="H258" s="17"/>
-      <c r="I258" s="7"/>
+      <c r="G258" s="12"/>
+      <c r="H258" s="7"/>
+      <c r="I258" s="17"/>
       <c r="J258" s="7"/>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -6990,17 +7288,18 @@
       <c r="T258" s="7"/>
       <c r="U258" s="7"/>
       <c r="V258" s="7"/>
-    </row>
-    <row r="259" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W258" s="7"/>
+    </row>
+    <row r="259" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="9"/>
       <c r="B259" s="5"/>
       <c r="C259" s="12"/>
       <c r="D259" s="12"/>
       <c r="E259" s="12"/>
       <c r="F259" s="12"/>
-      <c r="G259" s="7"/>
-      <c r="H259" s="17"/>
-      <c r="I259" s="7"/>
+      <c r="G259" s="12"/>
+      <c r="H259" s="7"/>
+      <c r="I259" s="17"/>
       <c r="J259" s="7"/>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -7014,17 +7313,18 @@
       <c r="T259" s="7"/>
       <c r="U259" s="7"/>
       <c r="V259" s="7"/>
-    </row>
-    <row r="260" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W259" s="7"/>
+    </row>
+    <row r="260" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="9"/>
       <c r="B260" s="5"/>
       <c r="C260" s="12"/>
       <c r="D260" s="12"/>
       <c r="E260" s="12"/>
       <c r="F260" s="12"/>
-      <c r="G260" s="7"/>
-      <c r="H260" s="17"/>
-      <c r="I260" s="7"/>
+      <c r="G260" s="12"/>
+      <c r="H260" s="7"/>
+      <c r="I260" s="17"/>
       <c r="J260" s="7"/>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -7038,17 +7338,18 @@
       <c r="T260" s="7"/>
       <c r="U260" s="7"/>
       <c r="V260" s="7"/>
-    </row>
-    <row r="261" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W260" s="7"/>
+    </row>
+    <row r="261" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="9"/>
       <c r="B261" s="5"/>
       <c r="C261" s="12"/>
       <c r="D261" s="12"/>
       <c r="E261" s="12"/>
       <c r="F261" s="12"/>
-      <c r="G261" s="7"/>
-      <c r="H261" s="17"/>
-      <c r="I261" s="7"/>
+      <c r="G261" s="12"/>
+      <c r="H261" s="7"/>
+      <c r="I261" s="17"/>
       <c r="J261" s="7"/>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -7062,17 +7363,18 @@
       <c r="T261" s="7"/>
       <c r="U261" s="7"/>
       <c r="V261" s="7"/>
-    </row>
-    <row r="262" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W261" s="7"/>
+    </row>
+    <row r="262" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="9"/>
       <c r="B262" s="5"/>
       <c r="C262" s="12"/>
       <c r="D262" s="12"/>
       <c r="E262" s="12"/>
       <c r="F262" s="12"/>
-      <c r="G262" s="7"/>
-      <c r="H262" s="17"/>
-      <c r="I262" s="7"/>
+      <c r="G262" s="12"/>
+      <c r="H262" s="7"/>
+      <c r="I262" s="17"/>
       <c r="J262" s="7"/>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -7086,17 +7388,18 @@
       <c r="T262" s="7"/>
       <c r="U262" s="7"/>
       <c r="V262" s="7"/>
-    </row>
-    <row r="263" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W262" s="7"/>
+    </row>
+    <row r="263" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="9"/>
       <c r="B263" s="5"/>
       <c r="C263" s="12"/>
       <c r="D263" s="12"/>
       <c r="E263" s="12"/>
       <c r="F263" s="12"/>
-      <c r="G263" s="7"/>
-      <c r="H263" s="17"/>
-      <c r="I263" s="7"/>
+      <c r="G263" s="12"/>
+      <c r="H263" s="7"/>
+      <c r="I263" s="17"/>
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -7110,17 +7413,18 @@
       <c r="T263" s="7"/>
       <c r="U263" s="7"/>
       <c r="V263" s="7"/>
-    </row>
-    <row r="264" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W263" s="7"/>
+    </row>
+    <row r="264" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="9"/>
       <c r="B264" s="5"/>
       <c r="C264" s="12"/>
       <c r="D264" s="12"/>
       <c r="E264" s="12"/>
       <c r="F264" s="12"/>
-      <c r="G264" s="7"/>
-      <c r="H264" s="17"/>
-      <c r="I264" s="7"/>
+      <c r="G264" s="12"/>
+      <c r="H264" s="7"/>
+      <c r="I264" s="17"/>
       <c r="J264" s="7"/>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -7134,17 +7438,18 @@
       <c r="T264" s="7"/>
       <c r="U264" s="7"/>
       <c r="V264" s="7"/>
-    </row>
-    <row r="265" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W264" s="7"/>
+    </row>
+    <row r="265" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="9"/>
       <c r="B265" s="5"/>
       <c r="C265" s="12"/>
       <c r="D265" s="12"/>
       <c r="E265" s="12"/>
       <c r="F265" s="12"/>
-      <c r="G265" s="7"/>
-      <c r="H265" s="17"/>
-      <c r="I265" s="7"/>
+      <c r="G265" s="12"/>
+      <c r="H265" s="7"/>
+      <c r="I265" s="17"/>
       <c r="J265" s="7"/>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -7158,17 +7463,18 @@
       <c r="T265" s="7"/>
       <c r="U265" s="7"/>
       <c r="V265" s="7"/>
-    </row>
-    <row r="266" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W265" s="7"/>
+    </row>
+    <row r="266" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="9"/>
       <c r="B266" s="5"/>
       <c r="C266" s="12"/>
       <c r="D266" s="12"/>
       <c r="E266" s="12"/>
       <c r="F266" s="12"/>
-      <c r="G266" s="7"/>
-      <c r="H266" s="17"/>
-      <c r="I266" s="7"/>
+      <c r="G266" s="12"/>
+      <c r="H266" s="7"/>
+      <c r="I266" s="17"/>
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -7182,17 +7488,18 @@
       <c r="T266" s="7"/>
       <c r="U266" s="7"/>
       <c r="V266" s="7"/>
-    </row>
-    <row r="267" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W266" s="7"/>
+    </row>
+    <row r="267" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="9"/>
       <c r="B267" s="5"/>
       <c r="C267" s="12"/>
       <c r="D267" s="12"/>
       <c r="E267" s="12"/>
       <c r="F267" s="12"/>
-      <c r="G267" s="7"/>
-      <c r="H267" s="17"/>
-      <c r="I267" s="7"/>
+      <c r="G267" s="12"/>
+      <c r="H267" s="7"/>
+      <c r="I267" s="17"/>
       <c r="J267" s="7"/>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -7206,17 +7513,18 @@
       <c r="T267" s="7"/>
       <c r="U267" s="7"/>
       <c r="V267" s="7"/>
-    </row>
-    <row r="268" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W267" s="7"/>
+    </row>
+    <row r="268" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="9"/>
       <c r="B268" s="5"/>
       <c r="C268" s="12"/>
       <c r="D268" s="12"/>
       <c r="E268" s="12"/>
       <c r="F268" s="12"/>
-      <c r="G268" s="7"/>
-      <c r="H268" s="17"/>
-      <c r="I268" s="7"/>
+      <c r="G268" s="12"/>
+      <c r="H268" s="7"/>
+      <c r="I268" s="17"/>
       <c r="J268" s="7"/>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -7230,17 +7538,18 @@
       <c r="T268" s="7"/>
       <c r="U268" s="7"/>
       <c r="V268" s="7"/>
-    </row>
-    <row r="269" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W268" s="7"/>
+    </row>
+    <row r="269" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="9"/>
       <c r="B269" s="5"/>
       <c r="C269" s="12"/>
       <c r="D269" s="12"/>
       <c r="E269" s="12"/>
       <c r="F269" s="12"/>
-      <c r="G269" s="7"/>
-      <c r="H269" s="17"/>
-      <c r="I269" s="7"/>
+      <c r="G269" s="12"/>
+      <c r="H269" s="7"/>
+      <c r="I269" s="17"/>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -7254,17 +7563,18 @@
       <c r="T269" s="7"/>
       <c r="U269" s="7"/>
       <c r="V269" s="7"/>
-    </row>
-    <row r="270" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W269" s="7"/>
+    </row>
+    <row r="270" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="9"/>
       <c r="B270" s="5"/>
       <c r="C270" s="12"/>
       <c r="D270" s="12"/>
       <c r="E270" s="12"/>
       <c r="F270" s="12"/>
-      <c r="G270" s="7"/>
-      <c r="H270" s="17"/>
-      <c r="I270" s="7"/>
+      <c r="G270" s="12"/>
+      <c r="H270" s="7"/>
+      <c r="I270" s="17"/>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -7278,17 +7588,18 @@
       <c r="T270" s="7"/>
       <c r="U270" s="7"/>
       <c r="V270" s="7"/>
-    </row>
-    <row r="271" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W270" s="7"/>
+    </row>
+    <row r="271" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="9"/>
       <c r="B271" s="5"/>
       <c r="C271" s="12"/>
       <c r="D271" s="12"/>
       <c r="E271" s="12"/>
       <c r="F271" s="12"/>
-      <c r="G271" s="7"/>
-      <c r="H271" s="17"/>
-      <c r="I271" s="7"/>
+      <c r="G271" s="12"/>
+      <c r="H271" s="7"/>
+      <c r="I271" s="17"/>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -7302,8 +7613,9 @@
       <c r="T271" s="7"/>
       <c r="U271" s="7"/>
       <c r="V271" s="7"/>
-    </row>
-    <row r="272" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="W271" s="7"/>
+    </row>
+    <row r="272" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
